--- a/planilha-fazenda/704-AGRO-Gestao-de-Gado.xlsx
+++ b/planilha-fazenda/704-AGRO-Gestao-de-Gado.xlsx
@@ -141,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -189,6 +189,8 @@
     <xf numFmtId="167" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -8790,7 +8792,7 @@
       <c r="A3" s="13" t="n"/>
       <c r="B3" s="14" t="n"/>
       <c r="C3" s="14" t="n"/>
-      <c r="D3" s="14" t="n"/>
+      <c r="D3" s="27" t="n"/>
       <c r="E3" s="15" t="n"/>
       <c r="F3" s="16" t="n"/>
       <c r="G3" s="16" t="n"/>
@@ -8815,7 +8817,7 @@
       <c r="A4" s="20" t="n"/>
       <c r="B4" s="21" t="n"/>
       <c r="C4" s="21" t="n"/>
-      <c r="D4" s="21" t="n"/>
+      <c r="D4" s="28" t="n"/>
       <c r="E4" s="22" t="n"/>
       <c r="F4" s="23" t="n"/>
       <c r="G4" s="23" t="n"/>
@@ -8840,7 +8842,7 @@
       <c r="A5" s="13" t="n"/>
       <c r="B5" s="14" t="n"/>
       <c r="C5" s="14" t="n"/>
-      <c r="D5" s="14" t="n"/>
+      <c r="D5" s="27" t="n"/>
       <c r="E5" s="15" t="n"/>
       <c r="F5" s="16" t="n"/>
       <c r="G5" s="16" t="n"/>
@@ -8865,7 +8867,7 @@
       <c r="A6" s="20" t="n"/>
       <c r="B6" s="21" t="n"/>
       <c r="C6" s="21" t="n"/>
-      <c r="D6" s="21" t="n"/>
+      <c r="D6" s="28" t="n"/>
       <c r="E6" s="22" t="n"/>
       <c r="F6" s="23" t="n"/>
       <c r="G6" s="23" t="n"/>
@@ -8890,7 +8892,7 @@
       <c r="A7" s="13" t="n"/>
       <c r="B7" s="14" t="n"/>
       <c r="C7" s="14" t="n"/>
-      <c r="D7" s="14" t="n"/>
+      <c r="D7" s="27" t="n"/>
       <c r="E7" s="15" t="n"/>
       <c r="F7" s="16" t="n"/>
       <c r="G7" s="16" t="n"/>
@@ -8915,7 +8917,7 @@
       <c r="A8" s="20" t="n"/>
       <c r="B8" s="21" t="n"/>
       <c r="C8" s="21" t="n"/>
-      <c r="D8" s="21" t="n"/>
+      <c r="D8" s="28" t="n"/>
       <c r="E8" s="22" t="n"/>
       <c r="F8" s="23" t="n"/>
       <c r="G8" s="23" t="n"/>
@@ -8940,7 +8942,7 @@
       <c r="A9" s="13" t="n"/>
       <c r="B9" s="14" t="n"/>
       <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
+      <c r="D9" s="27" t="n"/>
       <c r="E9" s="15" t="n"/>
       <c r="F9" s="16" t="n"/>
       <c r="G9" s="16" t="n"/>
@@ -8965,7 +8967,7 @@
       <c r="A10" s="20" t="n"/>
       <c r="B10" s="21" t="n"/>
       <c r="C10" s="21" t="n"/>
-      <c r="D10" s="21" t="n"/>
+      <c r="D10" s="28" t="n"/>
       <c r="E10" s="22" t="n"/>
       <c r="F10" s="23" t="n"/>
       <c r="G10" s="23" t="n"/>
@@ -8990,7 +8992,7 @@
       <c r="A11" s="13" t="n"/>
       <c r="B11" s="14" t="n"/>
       <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
+      <c r="D11" s="27" t="n"/>
       <c r="E11" s="15" t="n"/>
       <c r="F11" s="16" t="n"/>
       <c r="G11" s="16" t="n"/>
@@ -9015,7 +9017,7 @@
       <c r="A12" s="20" t="n"/>
       <c r="B12" s="21" t="n"/>
       <c r="C12" s="21" t="n"/>
-      <c r="D12" s="21" t="n"/>
+      <c r="D12" s="28" t="n"/>
       <c r="E12" s="22" t="n"/>
       <c r="F12" s="23" t="n"/>
       <c r="G12" s="23" t="n"/>
@@ -9040,7 +9042,7 @@
       <c r="A13" s="13" t="n"/>
       <c r="B13" s="14" t="n"/>
       <c r="C13" s="14" t="n"/>
-      <c r="D13" s="14" t="n"/>
+      <c r="D13" s="27" t="n"/>
       <c r="E13" s="15" t="n"/>
       <c r="F13" s="16" t="n"/>
       <c r="G13" s="16" t="n"/>
@@ -9065,7 +9067,7 @@
       <c r="A14" s="20" t="n"/>
       <c r="B14" s="21" t="n"/>
       <c r="C14" s="21" t="n"/>
-      <c r="D14" s="21" t="n"/>
+      <c r="D14" s="28" t="n"/>
       <c r="E14" s="22" t="n"/>
       <c r="F14" s="23" t="n"/>
       <c r="G14" s="23" t="n"/>
@@ -9090,7 +9092,7 @@
       <c r="A15" s="13" t="n"/>
       <c r="B15" s="14" t="n"/>
       <c r="C15" s="14" t="n"/>
-      <c r="D15" s="14" t="n"/>
+      <c r="D15" s="27" t="n"/>
       <c r="E15" s="15" t="n"/>
       <c r="F15" s="16" t="n"/>
       <c r="G15" s="16" t="n"/>
@@ -9115,7 +9117,7 @@
       <c r="A16" s="20" t="n"/>
       <c r="B16" s="21" t="n"/>
       <c r="C16" s="21" t="n"/>
-      <c r="D16" s="21" t="n"/>
+      <c r="D16" s="28" t="n"/>
       <c r="E16" s="22" t="n"/>
       <c r="F16" s="23" t="n"/>
       <c r="G16" s="23" t="n"/>
@@ -9140,7 +9142,7 @@
       <c r="A17" s="13" t="n"/>
       <c r="B17" s="14" t="n"/>
       <c r="C17" s="14" t="n"/>
-      <c r="D17" s="14" t="n"/>
+      <c r="D17" s="27" t="n"/>
       <c r="E17" s="15" t="n"/>
       <c r="F17" s="16" t="n"/>
       <c r="G17" s="16" t="n"/>
@@ -9165,7 +9167,7 @@
       <c r="A18" s="20" t="n"/>
       <c r="B18" s="21" t="n"/>
       <c r="C18" s="21" t="n"/>
-      <c r="D18" s="21" t="n"/>
+      <c r="D18" s="28" t="n"/>
       <c r="E18" s="22" t="n"/>
       <c r="F18" s="23" t="n"/>
       <c r="G18" s="23" t="n"/>
@@ -9190,7 +9192,7 @@
       <c r="A19" s="13" t="n"/>
       <c r="B19" s="14" t="n"/>
       <c r="C19" s="14" t="n"/>
-      <c r="D19" s="14" t="n"/>
+      <c r="D19" s="27" t="n"/>
       <c r="E19" s="15" t="n"/>
       <c r="F19" s="16" t="n"/>
       <c r="G19" s="16" t="n"/>
@@ -9215,7 +9217,7 @@
       <c r="A20" s="20" t="n"/>
       <c r="B20" s="21" t="n"/>
       <c r="C20" s="21" t="n"/>
-      <c r="D20" s="21" t="n"/>
+      <c r="D20" s="28" t="n"/>
       <c r="E20" s="22" t="n"/>
       <c r="F20" s="23" t="n"/>
       <c r="G20" s="23" t="n"/>
@@ -9240,7 +9242,7 @@
       <c r="A21" s="13" t="n"/>
       <c r="B21" s="14" t="n"/>
       <c r="C21" s="14" t="n"/>
-      <c r="D21" s="14" t="n"/>
+      <c r="D21" s="27" t="n"/>
       <c r="E21" s="15" t="n"/>
       <c r="F21" s="16" t="n"/>
       <c r="G21" s="16" t="n"/>
@@ -9265,7 +9267,7 @@
       <c r="A22" s="20" t="n"/>
       <c r="B22" s="21" t="n"/>
       <c r="C22" s="21" t="n"/>
-      <c r="D22" s="21" t="n"/>
+      <c r="D22" s="28" t="n"/>
       <c r="E22" s="22" t="n"/>
       <c r="F22" s="23" t="n"/>
       <c r="G22" s="23" t="n"/>
@@ -9290,7 +9292,7 @@
       <c r="A23" s="13" t="n"/>
       <c r="B23" s="14" t="n"/>
       <c r="C23" s="14" t="n"/>
-      <c r="D23" s="14" t="n"/>
+      <c r="D23" s="27" t="n"/>
       <c r="E23" s="15" t="n"/>
       <c r="F23" s="16" t="n"/>
       <c r="G23" s="16" t="n"/>
@@ -9315,7 +9317,7 @@
       <c r="A24" s="20" t="n"/>
       <c r="B24" s="21" t="n"/>
       <c r="C24" s="21" t="n"/>
-      <c r="D24" s="21" t="n"/>
+      <c r="D24" s="28" t="n"/>
       <c r="E24" s="22" t="n"/>
       <c r="F24" s="23" t="n"/>
       <c r="G24" s="23" t="n"/>
@@ -9340,7 +9342,7 @@
       <c r="A25" s="13" t="n"/>
       <c r="B25" s="14" t="n"/>
       <c r="C25" s="14" t="n"/>
-      <c r="D25" s="14" t="n"/>
+      <c r="D25" s="27" t="n"/>
       <c r="E25" s="15" t="n"/>
       <c r="F25" s="16" t="n"/>
       <c r="G25" s="16" t="n"/>
@@ -9365,7 +9367,7 @@
       <c r="A26" s="20" t="n"/>
       <c r="B26" s="21" t="n"/>
       <c r="C26" s="21" t="n"/>
-      <c r="D26" s="21" t="n"/>
+      <c r="D26" s="28" t="n"/>
       <c r="E26" s="22" t="n"/>
       <c r="F26" s="23" t="n"/>
       <c r="G26" s="23" t="n"/>
@@ -9390,7 +9392,7 @@
       <c r="A27" s="13" t="n"/>
       <c r="B27" s="14" t="n"/>
       <c r="C27" s="14" t="n"/>
-      <c r="D27" s="14" t="n"/>
+      <c r="D27" s="27" t="n"/>
       <c r="E27" s="15" t="n"/>
       <c r="F27" s="16" t="n"/>
       <c r="G27" s="16" t="n"/>
@@ -9415,7 +9417,7 @@
       <c r="A28" s="20" t="n"/>
       <c r="B28" s="21" t="n"/>
       <c r="C28" s="21" t="n"/>
-      <c r="D28" s="21" t="n"/>
+      <c r="D28" s="28" t="n"/>
       <c r="E28" s="22" t="n"/>
       <c r="F28" s="23" t="n"/>
       <c r="G28" s="23" t="n"/>
@@ -9440,7 +9442,7 @@
       <c r="A29" s="13" t="n"/>
       <c r="B29" s="14" t="n"/>
       <c r="C29" s="14" t="n"/>
-      <c r="D29" s="14" t="n"/>
+      <c r="D29" s="27" t="n"/>
       <c r="E29" s="15" t="n"/>
       <c r="F29" s="16" t="n"/>
       <c r="G29" s="16" t="n"/>
@@ -9465,7 +9467,7 @@
       <c r="A30" s="20" t="n"/>
       <c r="B30" s="21" t="n"/>
       <c r="C30" s="21" t="n"/>
-      <c r="D30" s="21" t="n"/>
+      <c r="D30" s="28" t="n"/>
       <c r="E30" s="22" t="n"/>
       <c r="F30" s="23" t="n"/>
       <c r="G30" s="23" t="n"/>
@@ -9490,7 +9492,7 @@
       <c r="A31" s="13" t="n"/>
       <c r="B31" s="14" t="n"/>
       <c r="C31" s="14" t="n"/>
-      <c r="D31" s="14" t="n"/>
+      <c r="D31" s="27" t="n"/>
       <c r="E31" s="15" t="n"/>
       <c r="F31" s="16" t="n"/>
       <c r="G31" s="16" t="n"/>
@@ -9515,7 +9517,7 @@
       <c r="A32" s="20" t="n"/>
       <c r="B32" s="21" t="n"/>
       <c r="C32" s="21" t="n"/>
-      <c r="D32" s="21" t="n"/>
+      <c r="D32" s="28" t="n"/>
       <c r="E32" s="22" t="n"/>
       <c r="F32" s="23" t="n"/>
       <c r="G32" s="23" t="n"/>
@@ -9540,7 +9542,7 @@
       <c r="A33" s="13" t="n"/>
       <c r="B33" s="14" t="n"/>
       <c r="C33" s="14" t="n"/>
-      <c r="D33" s="14" t="n"/>
+      <c r="D33" s="27" t="n"/>
       <c r="E33" s="15" t="n"/>
       <c r="F33" s="16" t="n"/>
       <c r="G33" s="16" t="n"/>
@@ -9565,7 +9567,7 @@
       <c r="A34" s="20" t="n"/>
       <c r="B34" s="21" t="n"/>
       <c r="C34" s="21" t="n"/>
-      <c r="D34" s="21" t="n"/>
+      <c r="D34" s="28" t="n"/>
       <c r="E34" s="22" t="n"/>
       <c r="F34" s="23" t="n"/>
       <c r="G34" s="23" t="n"/>
@@ -9590,7 +9592,7 @@
       <c r="A35" s="13" t="n"/>
       <c r="B35" s="14" t="n"/>
       <c r="C35" s="14" t="n"/>
-      <c r="D35" s="14" t="n"/>
+      <c r="D35" s="27" t="n"/>
       <c r="E35" s="15" t="n"/>
       <c r="F35" s="16" t="n"/>
       <c r="G35" s="16" t="n"/>
@@ -9615,7 +9617,7 @@
       <c r="A36" s="20" t="n"/>
       <c r="B36" s="21" t="n"/>
       <c r="C36" s="21" t="n"/>
-      <c r="D36" s="21" t="n"/>
+      <c r="D36" s="28" t="n"/>
       <c r="E36" s="22" t="n"/>
       <c r="F36" s="23" t="n"/>
       <c r="G36" s="23" t="n"/>
@@ -9640,7 +9642,7 @@
       <c r="A37" s="13" t="n"/>
       <c r="B37" s="14" t="n"/>
       <c r="C37" s="14" t="n"/>
-      <c r="D37" s="14" t="n"/>
+      <c r="D37" s="27" t="n"/>
       <c r="E37" s="15" t="n"/>
       <c r="F37" s="16" t="n"/>
       <c r="G37" s="16" t="n"/>
@@ -9665,7 +9667,7 @@
       <c r="A38" s="20" t="n"/>
       <c r="B38" s="21" t="n"/>
       <c r="C38" s="21" t="n"/>
-      <c r="D38" s="21" t="n"/>
+      <c r="D38" s="28" t="n"/>
       <c r="E38" s="22" t="n"/>
       <c r="F38" s="23" t="n"/>
       <c r="G38" s="23" t="n"/>
@@ -9690,7 +9692,7 @@
       <c r="A39" s="13" t="n"/>
       <c r="B39" s="14" t="n"/>
       <c r="C39" s="14" t="n"/>
-      <c r="D39" s="14" t="n"/>
+      <c r="D39" s="27" t="n"/>
       <c r="E39" s="15" t="n"/>
       <c r="F39" s="16" t="n"/>
       <c r="G39" s="16" t="n"/>
@@ -9715,7 +9717,7 @@
       <c r="A40" s="20" t="n"/>
       <c r="B40" s="21" t="n"/>
       <c r="C40" s="21" t="n"/>
-      <c r="D40" s="21" t="n"/>
+      <c r="D40" s="28" t="n"/>
       <c r="E40" s="22" t="n"/>
       <c r="F40" s="23" t="n"/>
       <c r="G40" s="23" t="n"/>
@@ -9740,7 +9742,7 @@
       <c r="A41" s="13" t="n"/>
       <c r="B41" s="14" t="n"/>
       <c r="C41" s="14" t="n"/>
-      <c r="D41" s="14" t="n"/>
+      <c r="D41" s="27" t="n"/>
       <c r="E41" s="15" t="n"/>
       <c r="F41" s="16" t="n"/>
       <c r="G41" s="16" t="n"/>
@@ -9765,7 +9767,7 @@
       <c r="A42" s="20" t="n"/>
       <c r="B42" s="21" t="n"/>
       <c r="C42" s="21" t="n"/>
-      <c r="D42" s="21" t="n"/>
+      <c r="D42" s="28" t="n"/>
       <c r="E42" s="22" t="n"/>
       <c r="F42" s="23" t="n"/>
       <c r="G42" s="23" t="n"/>
@@ -9790,7 +9792,7 @@
       <c r="A43" s="13" t="n"/>
       <c r="B43" s="14" t="n"/>
       <c r="C43" s="14" t="n"/>
-      <c r="D43" s="14" t="n"/>
+      <c r="D43" s="27" t="n"/>
       <c r="E43" s="15" t="n"/>
       <c r="F43" s="16" t="n"/>
       <c r="G43" s="16" t="n"/>
@@ -9815,7 +9817,7 @@
       <c r="A44" s="20" t="n"/>
       <c r="B44" s="21" t="n"/>
       <c r="C44" s="21" t="n"/>
-      <c r="D44" s="21" t="n"/>
+      <c r="D44" s="28" t="n"/>
       <c r="E44" s="22" t="n"/>
       <c r="F44" s="23" t="n"/>
       <c r="G44" s="23" t="n"/>
@@ -9840,7 +9842,7 @@
       <c r="A45" s="13" t="n"/>
       <c r="B45" s="14" t="n"/>
       <c r="C45" s="14" t="n"/>
-      <c r="D45" s="14" t="n"/>
+      <c r="D45" s="27" t="n"/>
       <c r="E45" s="15" t="n"/>
       <c r="F45" s="16" t="n"/>
       <c r="G45" s="16" t="n"/>
@@ -9865,7 +9867,7 @@
       <c r="A46" s="20" t="n"/>
       <c r="B46" s="21" t="n"/>
       <c r="C46" s="21" t="n"/>
-      <c r="D46" s="21" t="n"/>
+      <c r="D46" s="28" t="n"/>
       <c r="E46" s="22" t="n"/>
       <c r="F46" s="23" t="n"/>
       <c r="G46" s="23" t="n"/>
@@ -9890,7 +9892,7 @@
       <c r="A47" s="13" t="n"/>
       <c r="B47" s="14" t="n"/>
       <c r="C47" s="14" t="n"/>
-      <c r="D47" s="14" t="n"/>
+      <c r="D47" s="27" t="n"/>
       <c r="E47" s="15" t="n"/>
       <c r="F47" s="16" t="n"/>
       <c r="G47" s="16" t="n"/>
@@ -9915,7 +9917,7 @@
       <c r="A48" s="20" t="n"/>
       <c r="B48" s="21" t="n"/>
       <c r="C48" s="21" t="n"/>
-      <c r="D48" s="21" t="n"/>
+      <c r="D48" s="28" t="n"/>
       <c r="E48" s="22" t="n"/>
       <c r="F48" s="23" t="n"/>
       <c r="G48" s="23" t="n"/>
@@ -9940,7 +9942,7 @@
       <c r="A49" s="13" t="n"/>
       <c r="B49" s="14" t="n"/>
       <c r="C49" s="14" t="n"/>
-      <c r="D49" s="14" t="n"/>
+      <c r="D49" s="27" t="n"/>
       <c r="E49" s="15" t="n"/>
       <c r="F49" s="16" t="n"/>
       <c r="G49" s="16" t="n"/>
@@ -9965,7 +9967,7 @@
       <c r="A50" s="20" t="n"/>
       <c r="B50" s="21" t="n"/>
       <c r="C50" s="21" t="n"/>
-      <c r="D50" s="21" t="n"/>
+      <c r="D50" s="28" t="n"/>
       <c r="E50" s="22" t="n"/>
       <c r="F50" s="23" t="n"/>
       <c r="G50" s="23" t="n"/>
@@ -9990,7 +9992,7 @@
       <c r="A51" s="13" t="n"/>
       <c r="B51" s="14" t="n"/>
       <c r="C51" s="14" t="n"/>
-      <c r="D51" s="14" t="n"/>
+      <c r="D51" s="27" t="n"/>
       <c r="E51" s="15" t="n"/>
       <c r="F51" s="16" t="n"/>
       <c r="G51" s="16" t="n"/>
@@ -10015,7 +10017,7 @@
       <c r="A52" s="20" t="n"/>
       <c r="B52" s="21" t="n"/>
       <c r="C52" s="21" t="n"/>
-      <c r="D52" s="21" t="n"/>
+      <c r="D52" s="28" t="n"/>
       <c r="E52" s="22" t="n"/>
       <c r="F52" s="23" t="n"/>
       <c r="G52" s="23" t="n"/>
@@ -10040,7 +10042,7 @@
       <c r="A53" s="13" t="n"/>
       <c r="B53" s="14" t="n"/>
       <c r="C53" s="14" t="n"/>
-      <c r="D53" s="14" t="n"/>
+      <c r="D53" s="27" t="n"/>
       <c r="E53" s="15" t="n"/>
       <c r="F53" s="16" t="n"/>
       <c r="G53" s="16" t="n"/>
@@ -10065,7 +10067,7 @@
       <c r="A54" s="20" t="n"/>
       <c r="B54" s="21" t="n"/>
       <c r="C54" s="21" t="n"/>
-      <c r="D54" s="21" t="n"/>
+      <c r="D54" s="28" t="n"/>
       <c r="E54" s="22" t="n"/>
       <c r="F54" s="23" t="n"/>
       <c r="G54" s="23" t="n"/>
@@ -10090,7 +10092,7 @@
       <c r="A55" s="13" t="n"/>
       <c r="B55" s="14" t="n"/>
       <c r="C55" s="14" t="n"/>
-      <c r="D55" s="14" t="n"/>
+      <c r="D55" s="27" t="n"/>
       <c r="E55" s="15" t="n"/>
       <c r="F55" s="16" t="n"/>
       <c r="G55" s="16" t="n"/>
@@ -10115,7 +10117,7 @@
       <c r="A56" s="20" t="n"/>
       <c r="B56" s="21" t="n"/>
       <c r="C56" s="21" t="n"/>
-      <c r="D56" s="21" t="n"/>
+      <c r="D56" s="28" t="n"/>
       <c r="E56" s="22" t="n"/>
       <c r="F56" s="23" t="n"/>
       <c r="G56" s="23" t="n"/>
@@ -10140,7 +10142,7 @@
       <c r="A57" s="13" t="n"/>
       <c r="B57" s="14" t="n"/>
       <c r="C57" s="14" t="n"/>
-      <c r="D57" s="14" t="n"/>
+      <c r="D57" s="27" t="n"/>
       <c r="E57" s="15" t="n"/>
       <c r="F57" s="16" t="n"/>
       <c r="G57" s="16" t="n"/>
@@ -10165,7 +10167,7 @@
       <c r="A58" s="20" t="n"/>
       <c r="B58" s="21" t="n"/>
       <c r="C58" s="21" t="n"/>
-      <c r="D58" s="21" t="n"/>
+      <c r="D58" s="28" t="n"/>
       <c r="E58" s="22" t="n"/>
       <c r="F58" s="23" t="n"/>
       <c r="G58" s="23" t="n"/>
@@ -10190,7 +10192,7 @@
       <c r="A59" s="13" t="n"/>
       <c r="B59" s="14" t="n"/>
       <c r="C59" s="14" t="n"/>
-      <c r="D59" s="14" t="n"/>
+      <c r="D59" s="27" t="n"/>
       <c r="E59" s="15" t="n"/>
       <c r="F59" s="16" t="n"/>
       <c r="G59" s="16" t="n"/>
@@ -10215,7 +10217,7 @@
       <c r="A60" s="20" t="n"/>
       <c r="B60" s="21" t="n"/>
       <c r="C60" s="21" t="n"/>
-      <c r="D60" s="21" t="n"/>
+      <c r="D60" s="28" t="n"/>
       <c r="E60" s="22" t="n"/>
       <c r="F60" s="23" t="n"/>
       <c r="G60" s="23" t="n"/>
@@ -10240,7 +10242,7 @@
       <c r="A61" s="13" t="n"/>
       <c r="B61" s="14" t="n"/>
       <c r="C61" s="14" t="n"/>
-      <c r="D61" s="14" t="n"/>
+      <c r="D61" s="27" t="n"/>
       <c r="E61" s="15" t="n"/>
       <c r="F61" s="16" t="n"/>
       <c r="G61" s="16" t="n"/>
@@ -10265,7 +10267,7 @@
       <c r="A62" s="20" t="n"/>
       <c r="B62" s="21" t="n"/>
       <c r="C62" s="21" t="n"/>
-      <c r="D62" s="21" t="n"/>
+      <c r="D62" s="28" t="n"/>
       <c r="E62" s="22" t="n"/>
       <c r="F62" s="23" t="n"/>
       <c r="G62" s="23" t="n"/>
@@ -10290,7 +10292,7 @@
       <c r="A63" s="13" t="n"/>
       <c r="B63" s="14" t="n"/>
       <c r="C63" s="14" t="n"/>
-      <c r="D63" s="14" t="n"/>
+      <c r="D63" s="27" t="n"/>
       <c r="E63" s="15" t="n"/>
       <c r="F63" s="16" t="n"/>
       <c r="G63" s="16" t="n"/>
@@ -10315,7 +10317,7 @@
       <c r="A64" s="20" t="n"/>
       <c r="B64" s="21" t="n"/>
       <c r="C64" s="21" t="n"/>
-      <c r="D64" s="21" t="n"/>
+      <c r="D64" s="28" t="n"/>
       <c r="E64" s="22" t="n"/>
       <c r="F64" s="23" t="n"/>
       <c r="G64" s="23" t="n"/>
@@ -10340,7 +10342,7 @@
       <c r="A65" s="13" t="n"/>
       <c r="B65" s="14" t="n"/>
       <c r="C65" s="14" t="n"/>
-      <c r="D65" s="14" t="n"/>
+      <c r="D65" s="27" t="n"/>
       <c r="E65" s="15" t="n"/>
       <c r="F65" s="16" t="n"/>
       <c r="G65" s="16" t="n"/>
@@ -10365,7 +10367,7 @@
       <c r="A66" s="20" t="n"/>
       <c r="B66" s="21" t="n"/>
       <c r="C66" s="21" t="n"/>
-      <c r="D66" s="21" t="n"/>
+      <c r="D66" s="28" t="n"/>
       <c r="E66" s="22" t="n"/>
       <c r="F66" s="23" t="n"/>
       <c r="G66" s="23" t="n"/>
@@ -10390,7 +10392,7 @@
       <c r="A67" s="13" t="n"/>
       <c r="B67" s="14" t="n"/>
       <c r="C67" s="14" t="n"/>
-      <c r="D67" s="14" t="n"/>
+      <c r="D67" s="27" t="n"/>
       <c r="E67" s="15" t="n"/>
       <c r="F67" s="16" t="n"/>
       <c r="G67" s="16" t="n"/>
@@ -10415,7 +10417,7 @@
       <c r="A68" s="20" t="n"/>
       <c r="B68" s="21" t="n"/>
       <c r="C68" s="21" t="n"/>
-      <c r="D68" s="21" t="n"/>
+      <c r="D68" s="28" t="n"/>
       <c r="E68" s="22" t="n"/>
       <c r="F68" s="23" t="n"/>
       <c r="G68" s="23" t="n"/>
@@ -10440,7 +10442,7 @@
       <c r="A69" s="13" t="n"/>
       <c r="B69" s="14" t="n"/>
       <c r="C69" s="14" t="n"/>
-      <c r="D69" s="14" t="n"/>
+      <c r="D69" s="27" t="n"/>
       <c r="E69" s="15" t="n"/>
       <c r="F69" s="16" t="n"/>
       <c r="G69" s="16" t="n"/>
@@ -10465,7 +10467,7 @@
       <c r="A70" s="20" t="n"/>
       <c r="B70" s="21" t="n"/>
       <c r="C70" s="21" t="n"/>
-      <c r="D70" s="21" t="n"/>
+      <c r="D70" s="28" t="n"/>
       <c r="E70" s="22" t="n"/>
       <c r="F70" s="23" t="n"/>
       <c r="G70" s="23" t="n"/>
@@ -10490,7 +10492,7 @@
       <c r="A71" s="13" t="n"/>
       <c r="B71" s="14" t="n"/>
       <c r="C71" s="14" t="n"/>
-      <c r="D71" s="14" t="n"/>
+      <c r="D71" s="27" t="n"/>
       <c r="E71" s="15" t="n"/>
       <c r="F71" s="16" t="n"/>
       <c r="G71" s="16" t="n"/>
@@ -10515,7 +10517,7 @@
       <c r="A72" s="20" t="n"/>
       <c r="B72" s="21" t="n"/>
       <c r="C72" s="21" t="n"/>
-      <c r="D72" s="21" t="n"/>
+      <c r="D72" s="28" t="n"/>
       <c r="E72" s="22" t="n"/>
       <c r="F72" s="23" t="n"/>
       <c r="G72" s="23" t="n"/>
@@ -10540,7 +10542,7 @@
       <c r="A73" s="13" t="n"/>
       <c r="B73" s="14" t="n"/>
       <c r="C73" s="14" t="n"/>
-      <c r="D73" s="14" t="n"/>
+      <c r="D73" s="27" t="n"/>
       <c r="E73" s="15" t="n"/>
       <c r="F73" s="16" t="n"/>
       <c r="G73" s="16" t="n"/>
@@ -10565,7 +10567,7 @@
       <c r="A74" s="20" t="n"/>
       <c r="B74" s="21" t="n"/>
       <c r="C74" s="21" t="n"/>
-      <c r="D74" s="21" t="n"/>
+      <c r="D74" s="28" t="n"/>
       <c r="E74" s="22" t="n"/>
       <c r="F74" s="23" t="n"/>
       <c r="G74" s="23" t="n"/>
@@ -10590,7 +10592,7 @@
       <c r="A75" s="13" t="n"/>
       <c r="B75" s="14" t="n"/>
       <c r="C75" s="14" t="n"/>
-      <c r="D75" s="14" t="n"/>
+      <c r="D75" s="27" t="n"/>
       <c r="E75" s="15" t="n"/>
       <c r="F75" s="16" t="n"/>
       <c r="G75" s="16" t="n"/>
@@ -10615,7 +10617,7 @@
       <c r="A76" s="20" t="n"/>
       <c r="B76" s="21" t="n"/>
       <c r="C76" s="21" t="n"/>
-      <c r="D76" s="21" t="n"/>
+      <c r="D76" s="28" t="n"/>
       <c r="E76" s="22" t="n"/>
       <c r="F76" s="23" t="n"/>
       <c r="G76" s="23" t="n"/>
@@ -10640,7 +10642,7 @@
       <c r="A77" s="13" t="n"/>
       <c r="B77" s="14" t="n"/>
       <c r="C77" s="14" t="n"/>
-      <c r="D77" s="14" t="n"/>
+      <c r="D77" s="27" t="n"/>
       <c r="E77" s="15" t="n"/>
       <c r="F77" s="16" t="n"/>
       <c r="G77" s="16" t="n"/>
@@ -10665,7 +10667,7 @@
       <c r="A78" s="20" t="n"/>
       <c r="B78" s="21" t="n"/>
       <c r="C78" s="21" t="n"/>
-      <c r="D78" s="21" t="n"/>
+      <c r="D78" s="28" t="n"/>
       <c r="E78" s="22" t="n"/>
       <c r="F78" s="23" t="n"/>
       <c r="G78" s="23" t="n"/>
@@ -10690,7 +10692,7 @@
       <c r="A79" s="13" t="n"/>
       <c r="B79" s="14" t="n"/>
       <c r="C79" s="14" t="n"/>
-      <c r="D79" s="14" t="n"/>
+      <c r="D79" s="27" t="n"/>
       <c r="E79" s="15" t="n"/>
       <c r="F79" s="16" t="n"/>
       <c r="G79" s="16" t="n"/>
@@ -10715,7 +10717,7 @@
       <c r="A80" s="20" t="n"/>
       <c r="B80" s="21" t="n"/>
       <c r="C80" s="21" t="n"/>
-      <c r="D80" s="21" t="n"/>
+      <c r="D80" s="28" t="n"/>
       <c r="E80" s="22" t="n"/>
       <c r="F80" s="23" t="n"/>
       <c r="G80" s="23" t="n"/>
@@ -10740,7 +10742,7 @@
       <c r="A81" s="13" t="n"/>
       <c r="B81" s="14" t="n"/>
       <c r="C81" s="14" t="n"/>
-      <c r="D81" s="14" t="n"/>
+      <c r="D81" s="27" t="n"/>
       <c r="E81" s="15" t="n"/>
       <c r="F81" s="16" t="n"/>
       <c r="G81" s="16" t="n"/>
@@ -10765,7 +10767,7 @@
       <c r="A82" s="20" t="n"/>
       <c r="B82" s="21" t="n"/>
       <c r="C82" s="21" t="n"/>
-      <c r="D82" s="21" t="n"/>
+      <c r="D82" s="28" t="n"/>
       <c r="E82" s="22" t="n"/>
       <c r="F82" s="23" t="n"/>
       <c r="G82" s="23" t="n"/>
@@ -10790,7 +10792,7 @@
       <c r="A83" s="13" t="n"/>
       <c r="B83" s="14" t="n"/>
       <c r="C83" s="14" t="n"/>
-      <c r="D83" s="14" t="n"/>
+      <c r="D83" s="27" t="n"/>
       <c r="E83" s="15" t="n"/>
       <c r="F83" s="16" t="n"/>
       <c r="G83" s="16" t="n"/>
@@ -10815,7 +10817,7 @@
       <c r="A84" s="20" t="n"/>
       <c r="B84" s="21" t="n"/>
       <c r="C84" s="21" t="n"/>
-      <c r="D84" s="21" t="n"/>
+      <c r="D84" s="28" t="n"/>
       <c r="E84" s="22" t="n"/>
       <c r="F84" s="23" t="n"/>
       <c r="G84" s="23" t="n"/>
@@ -10840,7 +10842,7 @@
       <c r="A85" s="13" t="n"/>
       <c r="B85" s="14" t="n"/>
       <c r="C85" s="14" t="n"/>
-      <c r="D85" s="14" t="n"/>
+      <c r="D85" s="27" t="n"/>
       <c r="E85" s="15" t="n"/>
       <c r="F85" s="16" t="n"/>
       <c r="G85" s="16" t="n"/>
@@ -10865,7 +10867,7 @@
       <c r="A86" s="20" t="n"/>
       <c r="B86" s="21" t="n"/>
       <c r="C86" s="21" t="n"/>
-      <c r="D86" s="21" t="n"/>
+      <c r="D86" s="28" t="n"/>
       <c r="E86" s="22" t="n"/>
       <c r="F86" s="23" t="n"/>
       <c r="G86" s="23" t="n"/>
@@ -10890,7 +10892,7 @@
       <c r="A87" s="13" t="n"/>
       <c r="B87" s="14" t="n"/>
       <c r="C87" s="14" t="n"/>
-      <c r="D87" s="14" t="n"/>
+      <c r="D87" s="27" t="n"/>
       <c r="E87" s="15" t="n"/>
       <c r="F87" s="16" t="n"/>
       <c r="G87" s="16" t="n"/>
@@ -10915,7 +10917,7 @@
       <c r="A88" s="20" t="n"/>
       <c r="B88" s="21" t="n"/>
       <c r="C88" s="21" t="n"/>
-      <c r="D88" s="21" t="n"/>
+      <c r="D88" s="28" t="n"/>
       <c r="E88" s="22" t="n"/>
       <c r="F88" s="23" t="n"/>
       <c r="G88" s="23" t="n"/>
@@ -10940,7 +10942,7 @@
       <c r="A89" s="13" t="n"/>
       <c r="B89" s="14" t="n"/>
       <c r="C89" s="14" t="n"/>
-      <c r="D89" s="14" t="n"/>
+      <c r="D89" s="27" t="n"/>
       <c r="E89" s="15" t="n"/>
       <c r="F89" s="16" t="n"/>
       <c r="G89" s="16" t="n"/>
@@ -10965,7 +10967,7 @@
       <c r="A90" s="20" t="n"/>
       <c r="B90" s="21" t="n"/>
       <c r="C90" s="21" t="n"/>
-      <c r="D90" s="21" t="n"/>
+      <c r="D90" s="28" t="n"/>
       <c r="E90" s="22" t="n"/>
       <c r="F90" s="23" t="n"/>
       <c r="G90" s="23" t="n"/>
@@ -10990,7 +10992,7 @@
       <c r="A91" s="13" t="n"/>
       <c r="B91" s="14" t="n"/>
       <c r="C91" s="14" t="n"/>
-      <c r="D91" s="14" t="n"/>
+      <c r="D91" s="27" t="n"/>
       <c r="E91" s="15" t="n"/>
       <c r="F91" s="16" t="n"/>
       <c r="G91" s="16" t="n"/>
@@ -11015,7 +11017,7 @@
       <c r="A92" s="20" t="n"/>
       <c r="B92" s="21" t="n"/>
       <c r="C92" s="21" t="n"/>
-      <c r="D92" s="21" t="n"/>
+      <c r="D92" s="28" t="n"/>
       <c r="E92" s="22" t="n"/>
       <c r="F92" s="23" t="n"/>
       <c r="G92" s="23" t="n"/>
@@ -11040,7 +11042,7 @@
       <c r="A93" s="13" t="n"/>
       <c r="B93" s="14" t="n"/>
       <c r="C93" s="14" t="n"/>
-      <c r="D93" s="14" t="n"/>
+      <c r="D93" s="27" t="n"/>
       <c r="E93" s="15" t="n"/>
       <c r="F93" s="16" t="n"/>
       <c r="G93" s="16" t="n"/>
@@ -11065,7 +11067,7 @@
       <c r="A94" s="20" t="n"/>
       <c r="B94" s="21" t="n"/>
       <c r="C94" s="21" t="n"/>
-      <c r="D94" s="21" t="n"/>
+      <c r="D94" s="28" t="n"/>
       <c r="E94" s="22" t="n"/>
       <c r="F94" s="23" t="n"/>
       <c r="G94" s="23" t="n"/>
@@ -11090,7 +11092,7 @@
       <c r="A95" s="13" t="n"/>
       <c r="B95" s="14" t="n"/>
       <c r="C95" s="14" t="n"/>
-      <c r="D95" s="14" t="n"/>
+      <c r="D95" s="27" t="n"/>
       <c r="E95" s="15" t="n"/>
       <c r="F95" s="16" t="n"/>
       <c r="G95" s="16" t="n"/>
@@ -11115,7 +11117,7 @@
       <c r="A96" s="20" t="n"/>
       <c r="B96" s="21" t="n"/>
       <c r="C96" s="21" t="n"/>
-      <c r="D96" s="21" t="n"/>
+      <c r="D96" s="28" t="n"/>
       <c r="E96" s="22" t="n"/>
       <c r="F96" s="23" t="n"/>
       <c r="G96" s="23" t="n"/>
@@ -11140,7 +11142,7 @@
       <c r="A97" s="13" t="n"/>
       <c r="B97" s="14" t="n"/>
       <c r="C97" s="14" t="n"/>
-      <c r="D97" s="14" t="n"/>
+      <c r="D97" s="27" t="n"/>
       <c r="E97" s="15" t="n"/>
       <c r="F97" s="16" t="n"/>
       <c r="G97" s="16" t="n"/>
@@ -11165,7 +11167,7 @@
       <c r="A98" s="20" t="n"/>
       <c r="B98" s="21" t="n"/>
       <c r="C98" s="21" t="n"/>
-      <c r="D98" s="21" t="n"/>
+      <c r="D98" s="28" t="n"/>
       <c r="E98" s="22" t="n"/>
       <c r="F98" s="23" t="n"/>
       <c r="G98" s="23" t="n"/>
@@ -11190,7 +11192,7 @@
       <c r="A99" s="13" t="n"/>
       <c r="B99" s="14" t="n"/>
       <c r="C99" s="14" t="n"/>
-      <c r="D99" s="14" t="n"/>
+      <c r="D99" s="27" t="n"/>
       <c r="E99" s="15" t="n"/>
       <c r="F99" s="16" t="n"/>
       <c r="G99" s="16" t="n"/>
@@ -11215,7 +11217,7 @@
       <c r="A100" s="20" t="n"/>
       <c r="B100" s="21" t="n"/>
       <c r="C100" s="21" t="n"/>
-      <c r="D100" s="21" t="n"/>
+      <c r="D100" s="28" t="n"/>
       <c r="E100" s="22" t="n"/>
       <c r="F100" s="23" t="n"/>
       <c r="G100" s="23" t="n"/>
@@ -11240,7 +11242,7 @@
       <c r="A101" s="13" t="n"/>
       <c r="B101" s="14" t="n"/>
       <c r="C101" s="14" t="n"/>
-      <c r="D101" s="14" t="n"/>
+      <c r="D101" s="27" t="n"/>
       <c r="E101" s="15" t="n"/>
       <c r="F101" s="16" t="n"/>
       <c r="G101" s="16" t="n"/>
@@ -11265,7 +11267,7 @@
       <c r="A102" s="20" t="n"/>
       <c r="B102" s="21" t="n"/>
       <c r="C102" s="21" t="n"/>
-      <c r="D102" s="21" t="n"/>
+      <c r="D102" s="28" t="n"/>
       <c r="E102" s="22" t="n"/>
       <c r="F102" s="23" t="n"/>
       <c r="G102" s="23" t="n"/>
@@ -11290,7 +11292,7 @@
       <c r="A103" s="13" t="n"/>
       <c r="B103" s="14" t="n"/>
       <c r="C103" s="14" t="n"/>
-      <c r="D103" s="14" t="n"/>
+      <c r="D103" s="27" t="n"/>
       <c r="E103" s="15" t="n"/>
       <c r="F103" s="16" t="n"/>
       <c r="G103" s="16" t="n"/>
@@ -11315,7 +11317,7 @@
       <c r="A104" s="20" t="n"/>
       <c r="B104" s="21" t="n"/>
       <c r="C104" s="21" t="n"/>
-      <c r="D104" s="21" t="n"/>
+      <c r="D104" s="28" t="n"/>
       <c r="E104" s="22" t="n"/>
       <c r="F104" s="23" t="n"/>
       <c r="G104" s="23" t="n"/>
@@ -11340,7 +11342,7 @@
       <c r="A105" s="13" t="n"/>
       <c r="B105" s="14" t="n"/>
       <c r="C105" s="14" t="n"/>
-      <c r="D105" s="14" t="n"/>
+      <c r="D105" s="27" t="n"/>
       <c r="E105" s="15" t="n"/>
       <c r="F105" s="16" t="n"/>
       <c r="G105" s="16" t="n"/>
@@ -11365,7 +11367,7 @@
       <c r="A106" s="20" t="n"/>
       <c r="B106" s="21" t="n"/>
       <c r="C106" s="21" t="n"/>
-      <c r="D106" s="21" t="n"/>
+      <c r="D106" s="28" t="n"/>
       <c r="E106" s="22" t="n"/>
       <c r="F106" s="23" t="n"/>
       <c r="G106" s="23" t="n"/>
@@ -11390,7 +11392,7 @@
       <c r="A107" s="13" t="n"/>
       <c r="B107" s="14" t="n"/>
       <c r="C107" s="14" t="n"/>
-      <c r="D107" s="14" t="n"/>
+      <c r="D107" s="27" t="n"/>
       <c r="E107" s="15" t="n"/>
       <c r="F107" s="16" t="n"/>
       <c r="G107" s="16" t="n"/>
@@ -11415,7 +11417,7 @@
       <c r="A108" s="20" t="n"/>
       <c r="B108" s="21" t="n"/>
       <c r="C108" s="21" t="n"/>
-      <c r="D108" s="21" t="n"/>
+      <c r="D108" s="28" t="n"/>
       <c r="E108" s="22" t="n"/>
       <c r="F108" s="23" t="n"/>
       <c r="G108" s="23" t="n"/>
@@ -11440,7 +11442,7 @@
       <c r="A109" s="13" t="n"/>
       <c r="B109" s="14" t="n"/>
       <c r="C109" s="14" t="n"/>
-      <c r="D109" s="14" t="n"/>
+      <c r="D109" s="27" t="n"/>
       <c r="E109" s="15" t="n"/>
       <c r="F109" s="16" t="n"/>
       <c r="G109" s="16" t="n"/>
@@ -11465,7 +11467,7 @@
       <c r="A110" s="20" t="n"/>
       <c r="B110" s="21" t="n"/>
       <c r="C110" s="21" t="n"/>
-      <c r="D110" s="21" t="n"/>
+      <c r="D110" s="28" t="n"/>
       <c r="E110" s="22" t="n"/>
       <c r="F110" s="23" t="n"/>
       <c r="G110" s="23" t="n"/>
@@ -11490,7 +11492,7 @@
       <c r="A111" s="13" t="n"/>
       <c r="B111" s="14" t="n"/>
       <c r="C111" s="14" t="n"/>
-      <c r="D111" s="14" t="n"/>
+      <c r="D111" s="27" t="n"/>
       <c r="E111" s="15" t="n"/>
       <c r="F111" s="16" t="n"/>
       <c r="G111" s="16" t="n"/>
@@ -11515,7 +11517,7 @@
       <c r="A112" s="20" t="n"/>
       <c r="B112" s="21" t="n"/>
       <c r="C112" s="21" t="n"/>
-      <c r="D112" s="21" t="n"/>
+      <c r="D112" s="28" t="n"/>
       <c r="E112" s="22" t="n"/>
       <c r="F112" s="23" t="n"/>
       <c r="G112" s="23" t="n"/>
@@ -11540,7 +11542,7 @@
       <c r="A113" s="13" t="n"/>
       <c r="B113" s="14" t="n"/>
       <c r="C113" s="14" t="n"/>
-      <c r="D113" s="14" t="n"/>
+      <c r="D113" s="27" t="n"/>
       <c r="E113" s="15" t="n"/>
       <c r="F113" s="16" t="n"/>
       <c r="G113" s="16" t="n"/>
@@ -11565,7 +11567,7 @@
       <c r="A114" s="20" t="n"/>
       <c r="B114" s="21" t="n"/>
       <c r="C114" s="21" t="n"/>
-      <c r="D114" s="21" t="n"/>
+      <c r="D114" s="28" t="n"/>
       <c r="E114" s="22" t="n"/>
       <c r="F114" s="23" t="n"/>
       <c r="G114" s="23" t="n"/>
@@ -11590,7 +11592,7 @@
       <c r="A115" s="13" t="n"/>
       <c r="B115" s="14" t="n"/>
       <c r="C115" s="14" t="n"/>
-      <c r="D115" s="14" t="n"/>
+      <c r="D115" s="27" t="n"/>
       <c r="E115" s="15" t="n"/>
       <c r="F115" s="16" t="n"/>
       <c r="G115" s="16" t="n"/>
@@ -11615,7 +11617,7 @@
       <c r="A116" s="20" t="n"/>
       <c r="B116" s="21" t="n"/>
       <c r="C116" s="21" t="n"/>
-      <c r="D116" s="21" t="n"/>
+      <c r="D116" s="28" t="n"/>
       <c r="E116" s="22" t="n"/>
       <c r="F116" s="23" t="n"/>
       <c r="G116" s="23" t="n"/>
@@ -11640,7 +11642,7 @@
       <c r="A117" s="13" t="n"/>
       <c r="B117" s="14" t="n"/>
       <c r="C117" s="14" t="n"/>
-      <c r="D117" s="14" t="n"/>
+      <c r="D117" s="27" t="n"/>
       <c r="E117" s="15" t="n"/>
       <c r="F117" s="16" t="n"/>
       <c r="G117" s="16" t="n"/>
@@ -11665,7 +11667,7 @@
       <c r="A118" s="20" t="n"/>
       <c r="B118" s="21" t="n"/>
       <c r="C118" s="21" t="n"/>
-      <c r="D118" s="21" t="n"/>
+      <c r="D118" s="28" t="n"/>
       <c r="E118" s="22" t="n"/>
       <c r="F118" s="23" t="n"/>
       <c r="G118" s="23" t="n"/>
@@ -11690,7 +11692,7 @@
       <c r="A119" s="13" t="n"/>
       <c r="B119" s="14" t="n"/>
       <c r="C119" s="14" t="n"/>
-      <c r="D119" s="14" t="n"/>
+      <c r="D119" s="27" t="n"/>
       <c r="E119" s="15" t="n"/>
       <c r="F119" s="16" t="n"/>
       <c r="G119" s="16" t="n"/>
@@ -11715,7 +11717,7 @@
       <c r="A120" s="20" t="n"/>
       <c r="B120" s="21" t="n"/>
       <c r="C120" s="21" t="n"/>
-      <c r="D120" s="21" t="n"/>
+      <c r="D120" s="28" t="n"/>
       <c r="E120" s="22" t="n"/>
       <c r="F120" s="23" t="n"/>
       <c r="G120" s="23" t="n"/>
@@ -11740,7 +11742,7 @@
       <c r="A121" s="13" t="n"/>
       <c r="B121" s="14" t="n"/>
       <c r="C121" s="14" t="n"/>
-      <c r="D121" s="14" t="n"/>
+      <c r="D121" s="27" t="n"/>
       <c r="E121" s="15" t="n"/>
       <c r="F121" s="16" t="n"/>
       <c r="G121" s="16" t="n"/>
@@ -11765,7 +11767,7 @@
       <c r="A122" s="20" t="n"/>
       <c r="B122" s="21" t="n"/>
       <c r="C122" s="21" t="n"/>
-      <c r="D122" s="21" t="n"/>
+      <c r="D122" s="28" t="n"/>
       <c r="E122" s="22" t="n"/>
       <c r="F122" s="23" t="n"/>
       <c r="G122" s="23" t="n"/>
@@ -11790,7 +11792,7 @@
       <c r="A123" s="13" t="n"/>
       <c r="B123" s="14" t="n"/>
       <c r="C123" s="14" t="n"/>
-      <c r="D123" s="14" t="n"/>
+      <c r="D123" s="27" t="n"/>
       <c r="E123" s="15" t="n"/>
       <c r="F123" s="16" t="n"/>
       <c r="G123" s="16" t="n"/>
@@ -11815,7 +11817,7 @@
       <c r="A124" s="20" t="n"/>
       <c r="B124" s="21" t="n"/>
       <c r="C124" s="21" t="n"/>
-      <c r="D124" s="21" t="n"/>
+      <c r="D124" s="28" t="n"/>
       <c r="E124" s="22" t="n"/>
       <c r="F124" s="23" t="n"/>
       <c r="G124" s="23" t="n"/>
@@ -11840,7 +11842,7 @@
       <c r="A125" s="13" t="n"/>
       <c r="B125" s="14" t="n"/>
       <c r="C125" s="14" t="n"/>
-      <c r="D125" s="14" t="n"/>
+      <c r="D125" s="27" t="n"/>
       <c r="E125" s="15" t="n"/>
       <c r="F125" s="16" t="n"/>
       <c r="G125" s="16" t="n"/>
@@ -11865,7 +11867,7 @@
       <c r="A126" s="20" t="n"/>
       <c r="B126" s="21" t="n"/>
       <c r="C126" s="21" t="n"/>
-      <c r="D126" s="21" t="n"/>
+      <c r="D126" s="28" t="n"/>
       <c r="E126" s="22" t="n"/>
       <c r="F126" s="23" t="n"/>
       <c r="G126" s="23" t="n"/>
@@ -11890,7 +11892,7 @@
       <c r="A127" s="13" t="n"/>
       <c r="B127" s="14" t="n"/>
       <c r="C127" s="14" t="n"/>
-      <c r="D127" s="14" t="n"/>
+      <c r="D127" s="27" t="n"/>
       <c r="E127" s="15" t="n"/>
       <c r="F127" s="16" t="n"/>
       <c r="G127" s="16" t="n"/>
@@ -11915,7 +11917,7 @@
       <c r="A128" s="20" t="n"/>
       <c r="B128" s="21" t="n"/>
       <c r="C128" s="21" t="n"/>
-      <c r="D128" s="21" t="n"/>
+      <c r="D128" s="28" t="n"/>
       <c r="E128" s="22" t="n"/>
       <c r="F128" s="23" t="n"/>
       <c r="G128" s="23" t="n"/>
@@ -11940,7 +11942,7 @@
       <c r="A129" s="13" t="n"/>
       <c r="B129" s="14" t="n"/>
       <c r="C129" s="14" t="n"/>
-      <c r="D129" s="14" t="n"/>
+      <c r="D129" s="27" t="n"/>
       <c r="E129" s="15" t="n"/>
       <c r="F129" s="16" t="n"/>
       <c r="G129" s="16" t="n"/>
@@ -11965,7 +11967,7 @@
       <c r="A130" s="20" t="n"/>
       <c r="B130" s="21" t="n"/>
       <c r="C130" s="21" t="n"/>
-      <c r="D130" s="21" t="n"/>
+      <c r="D130" s="28" t="n"/>
       <c r="E130" s="22" t="n"/>
       <c r="F130" s="23" t="n"/>
       <c r="G130" s="23" t="n"/>
@@ -11990,7 +11992,7 @@
       <c r="A131" s="13" t="n"/>
       <c r="B131" s="14" t="n"/>
       <c r="C131" s="14" t="n"/>
-      <c r="D131" s="14" t="n"/>
+      <c r="D131" s="27" t="n"/>
       <c r="E131" s="15" t="n"/>
       <c r="F131" s="16" t="n"/>
       <c r="G131" s="16" t="n"/>
@@ -12015,7 +12017,7 @@
       <c r="A132" s="20" t="n"/>
       <c r="B132" s="21" t="n"/>
       <c r="C132" s="21" t="n"/>
-      <c r="D132" s="21" t="n"/>
+      <c r="D132" s="28" t="n"/>
       <c r="E132" s="22" t="n"/>
       <c r="F132" s="23" t="n"/>
       <c r="G132" s="23" t="n"/>
@@ -12040,7 +12042,7 @@
       <c r="A133" s="13" t="n"/>
       <c r="B133" s="14" t="n"/>
       <c r="C133" s="14" t="n"/>
-      <c r="D133" s="14" t="n"/>
+      <c r="D133" s="27" t="n"/>
       <c r="E133" s="15" t="n"/>
       <c r="F133" s="16" t="n"/>
       <c r="G133" s="16" t="n"/>
@@ -12065,7 +12067,7 @@
       <c r="A134" s="20" t="n"/>
       <c r="B134" s="21" t="n"/>
       <c r="C134" s="21" t="n"/>
-      <c r="D134" s="21" t="n"/>
+      <c r="D134" s="28" t="n"/>
       <c r="E134" s="22" t="n"/>
       <c r="F134" s="23" t="n"/>
       <c r="G134" s="23" t="n"/>
@@ -12090,7 +12092,7 @@
       <c r="A135" s="13" t="n"/>
       <c r="B135" s="14" t="n"/>
       <c r="C135" s="14" t="n"/>
-      <c r="D135" s="14" t="n"/>
+      <c r="D135" s="27" t="n"/>
       <c r="E135" s="15" t="n"/>
       <c r="F135" s="16" t="n"/>
       <c r="G135" s="16" t="n"/>
@@ -12115,7 +12117,7 @@
       <c r="A136" s="20" t="n"/>
       <c r="B136" s="21" t="n"/>
       <c r="C136" s="21" t="n"/>
-      <c r="D136" s="21" t="n"/>
+      <c r="D136" s="28" t="n"/>
       <c r="E136" s="22" t="n"/>
       <c r="F136" s="23" t="n"/>
       <c r="G136" s="23" t="n"/>
@@ -12140,7 +12142,7 @@
       <c r="A137" s="13" t="n"/>
       <c r="B137" s="14" t="n"/>
       <c r="C137" s="14" t="n"/>
-      <c r="D137" s="14" t="n"/>
+      <c r="D137" s="27" t="n"/>
       <c r="E137" s="15" t="n"/>
       <c r="F137" s="16" t="n"/>
       <c r="G137" s="16" t="n"/>
@@ -12165,7 +12167,7 @@
       <c r="A138" s="20" t="n"/>
       <c r="B138" s="21" t="n"/>
       <c r="C138" s="21" t="n"/>
-      <c r="D138" s="21" t="n"/>
+      <c r="D138" s="28" t="n"/>
       <c r="E138" s="22" t="n"/>
       <c r="F138" s="23" t="n"/>
       <c r="G138" s="23" t="n"/>
@@ -12190,7 +12192,7 @@
       <c r="A139" s="13" t="n"/>
       <c r="B139" s="14" t="n"/>
       <c r="C139" s="14" t="n"/>
-      <c r="D139" s="14" t="n"/>
+      <c r="D139" s="27" t="n"/>
       <c r="E139" s="15" t="n"/>
       <c r="F139" s="16" t="n"/>
       <c r="G139" s="16" t="n"/>
@@ -12215,7 +12217,7 @@
       <c r="A140" s="20" t="n"/>
       <c r="B140" s="21" t="n"/>
       <c r="C140" s="21" t="n"/>
-      <c r="D140" s="21" t="n"/>
+      <c r="D140" s="28" t="n"/>
       <c r="E140" s="22" t="n"/>
       <c r="F140" s="23" t="n"/>
       <c r="G140" s="23" t="n"/>
@@ -12240,7 +12242,7 @@
       <c r="A141" s="13" t="n"/>
       <c r="B141" s="14" t="n"/>
       <c r="C141" s="14" t="n"/>
-      <c r="D141" s="14" t="n"/>
+      <c r="D141" s="27" t="n"/>
       <c r="E141" s="15" t="n"/>
       <c r="F141" s="16" t="n"/>
       <c r="G141" s="16" t="n"/>
@@ -12265,7 +12267,7 @@
       <c r="A142" s="20" t="n"/>
       <c r="B142" s="21" t="n"/>
       <c r="C142" s="21" t="n"/>
-      <c r="D142" s="21" t="n"/>
+      <c r="D142" s="28" t="n"/>
       <c r="E142" s="22" t="n"/>
       <c r="F142" s="23" t="n"/>
       <c r="G142" s="23" t="n"/>
@@ -12290,7 +12292,7 @@
       <c r="A143" s="13" t="n"/>
       <c r="B143" s="14" t="n"/>
       <c r="C143" s="14" t="n"/>
-      <c r="D143" s="14" t="n"/>
+      <c r="D143" s="27" t="n"/>
       <c r="E143" s="15" t="n"/>
       <c r="F143" s="16" t="n"/>
       <c r="G143" s="16" t="n"/>
@@ -12315,7 +12317,7 @@
       <c r="A144" s="20" t="n"/>
       <c r="B144" s="21" t="n"/>
       <c r="C144" s="21" t="n"/>
-      <c r="D144" s="21" t="n"/>
+      <c r="D144" s="28" t="n"/>
       <c r="E144" s="22" t="n"/>
       <c r="F144" s="23" t="n"/>
       <c r="G144" s="23" t="n"/>
@@ -12340,7 +12342,7 @@
       <c r="A145" s="13" t="n"/>
       <c r="B145" s="14" t="n"/>
       <c r="C145" s="14" t="n"/>
-      <c r="D145" s="14" t="n"/>
+      <c r="D145" s="27" t="n"/>
       <c r="E145" s="15" t="n"/>
       <c r="F145" s="16" t="n"/>
       <c r="G145" s="16" t="n"/>
@@ -12365,7 +12367,7 @@
       <c r="A146" s="20" t="n"/>
       <c r="B146" s="21" t="n"/>
       <c r="C146" s="21" t="n"/>
-      <c r="D146" s="21" t="n"/>
+      <c r="D146" s="28" t="n"/>
       <c r="E146" s="22" t="n"/>
       <c r="F146" s="23" t="n"/>
       <c r="G146" s="23" t="n"/>
@@ -12390,7 +12392,7 @@
       <c r="A147" s="13" t="n"/>
       <c r="B147" s="14" t="n"/>
       <c r="C147" s="14" t="n"/>
-      <c r="D147" s="14" t="n"/>
+      <c r="D147" s="27" t="n"/>
       <c r="E147" s="15" t="n"/>
       <c r="F147" s="16" t="n"/>
       <c r="G147" s="16" t="n"/>
@@ -12415,7 +12417,7 @@
       <c r="A148" s="20" t="n"/>
       <c r="B148" s="21" t="n"/>
       <c r="C148" s="21" t="n"/>
-      <c r="D148" s="21" t="n"/>
+      <c r="D148" s="28" t="n"/>
       <c r="E148" s="22" t="n"/>
       <c r="F148" s="23" t="n"/>
       <c r="G148" s="23" t="n"/>
@@ -12440,7 +12442,7 @@
       <c r="A149" s="13" t="n"/>
       <c r="B149" s="14" t="n"/>
       <c r="C149" s="14" t="n"/>
-      <c r="D149" s="14" t="n"/>
+      <c r="D149" s="27" t="n"/>
       <c r="E149" s="15" t="n"/>
       <c r="F149" s="16" t="n"/>
       <c r="G149" s="16" t="n"/>
@@ -12465,7 +12467,7 @@
       <c r="A150" s="20" t="n"/>
       <c r="B150" s="21" t="n"/>
       <c r="C150" s="21" t="n"/>
-      <c r="D150" s="21" t="n"/>
+      <c r="D150" s="28" t="n"/>
       <c r="E150" s="22" t="n"/>
       <c r="F150" s="23" t="n"/>
       <c r="G150" s="23" t="n"/>
@@ -12490,7 +12492,7 @@
       <c r="A151" s="13" t="n"/>
       <c r="B151" s="14" t="n"/>
       <c r="C151" s="14" t="n"/>
-      <c r="D151" s="14" t="n"/>
+      <c r="D151" s="27" t="n"/>
       <c r="E151" s="15" t="n"/>
       <c r="F151" s="16" t="n"/>
       <c r="G151" s="16" t="n"/>
@@ -12515,7 +12517,7 @@
       <c r="A152" s="20" t="n"/>
       <c r="B152" s="21" t="n"/>
       <c r="C152" s="21" t="n"/>
-      <c r="D152" s="21" t="n"/>
+      <c r="D152" s="28" t="n"/>
       <c r="E152" s="22" t="n"/>
       <c r="F152" s="23" t="n"/>
       <c r="G152" s="23" t="n"/>
@@ -12540,7 +12542,7 @@
       <c r="A153" s="13" t="n"/>
       <c r="B153" s="14" t="n"/>
       <c r="C153" s="14" t="n"/>
-      <c r="D153" s="14" t="n"/>
+      <c r="D153" s="27" t="n"/>
       <c r="E153" s="15" t="n"/>
       <c r="F153" s="16" t="n"/>
       <c r="G153" s="16" t="n"/>
@@ -12565,7 +12567,7 @@
       <c r="A154" s="20" t="n"/>
       <c r="B154" s="21" t="n"/>
       <c r="C154" s="21" t="n"/>
-      <c r="D154" s="21" t="n"/>
+      <c r="D154" s="28" t="n"/>
       <c r="E154" s="22" t="n"/>
       <c r="F154" s="23" t="n"/>
       <c r="G154" s="23" t="n"/>
@@ -12590,7 +12592,7 @@
       <c r="A155" s="13" t="n"/>
       <c r="B155" s="14" t="n"/>
       <c r="C155" s="14" t="n"/>
-      <c r="D155" s="14" t="n"/>
+      <c r="D155" s="27" t="n"/>
       <c r="E155" s="15" t="n"/>
       <c r="F155" s="16" t="n"/>
       <c r="G155" s="16" t="n"/>
@@ -12615,7 +12617,7 @@
       <c r="A156" s="20" t="n"/>
       <c r="B156" s="21" t="n"/>
       <c r="C156" s="21" t="n"/>
-      <c r="D156" s="21" t="n"/>
+      <c r="D156" s="28" t="n"/>
       <c r="E156" s="22" t="n"/>
       <c r="F156" s="23" t="n"/>
       <c r="G156" s="23" t="n"/>
@@ -12640,7 +12642,7 @@
       <c r="A157" s="13" t="n"/>
       <c r="B157" s="14" t="n"/>
       <c r="C157" s="14" t="n"/>
-      <c r="D157" s="14" t="n"/>
+      <c r="D157" s="27" t="n"/>
       <c r="E157" s="15" t="n"/>
       <c r="F157" s="16" t="n"/>
       <c r="G157" s="16" t="n"/>
@@ -12665,7 +12667,7 @@
       <c r="A158" s="20" t="n"/>
       <c r="B158" s="21" t="n"/>
       <c r="C158" s="21" t="n"/>
-      <c r="D158" s="21" t="n"/>
+      <c r="D158" s="28" t="n"/>
       <c r="E158" s="22" t="n"/>
       <c r="F158" s="23" t="n"/>
       <c r="G158" s="23" t="n"/>
@@ -12690,7 +12692,7 @@
       <c r="A159" s="13" t="n"/>
       <c r="B159" s="14" t="n"/>
       <c r="C159" s="14" t="n"/>
-      <c r="D159" s="14" t="n"/>
+      <c r="D159" s="27" t="n"/>
       <c r="E159" s="15" t="n"/>
       <c r="F159" s="16" t="n"/>
       <c r="G159" s="16" t="n"/>
@@ -12715,7 +12717,7 @@
       <c r="A160" s="20" t="n"/>
       <c r="B160" s="21" t="n"/>
       <c r="C160" s="21" t="n"/>
-      <c r="D160" s="21" t="n"/>
+      <c r="D160" s="28" t="n"/>
       <c r="E160" s="22" t="n"/>
       <c r="F160" s="23" t="n"/>
       <c r="G160" s="23" t="n"/>
@@ -12740,7 +12742,7 @@
       <c r="A161" s="13" t="n"/>
       <c r="B161" s="14" t="n"/>
       <c r="C161" s="14" t="n"/>
-      <c r="D161" s="14" t="n"/>
+      <c r="D161" s="27" t="n"/>
       <c r="E161" s="15" t="n"/>
       <c r="F161" s="16" t="n"/>
       <c r="G161" s="16" t="n"/>
@@ -12765,7 +12767,7 @@
       <c r="A162" s="20" t="n"/>
       <c r="B162" s="21" t="n"/>
       <c r="C162" s="21" t="n"/>
-      <c r="D162" s="21" t="n"/>
+      <c r="D162" s="28" t="n"/>
       <c r="E162" s="22" t="n"/>
       <c r="F162" s="23" t="n"/>
       <c r="G162" s="23" t="n"/>
@@ -12790,7 +12792,7 @@
       <c r="A163" s="13" t="n"/>
       <c r="B163" s="14" t="n"/>
       <c r="C163" s="14" t="n"/>
-      <c r="D163" s="14" t="n"/>
+      <c r="D163" s="27" t="n"/>
       <c r="E163" s="15" t="n"/>
       <c r="F163" s="16" t="n"/>
       <c r="G163" s="16" t="n"/>
@@ -12815,7 +12817,7 @@
       <c r="A164" s="20" t="n"/>
       <c r="B164" s="21" t="n"/>
       <c r="C164" s="21" t="n"/>
-      <c r="D164" s="21" t="n"/>
+      <c r="D164" s="28" t="n"/>
       <c r="E164" s="22" t="n"/>
       <c r="F164" s="23" t="n"/>
       <c r="G164" s="23" t="n"/>
@@ -12840,7 +12842,7 @@
       <c r="A165" s="13" t="n"/>
       <c r="B165" s="14" t="n"/>
       <c r="C165" s="14" t="n"/>
-      <c r="D165" s="14" t="n"/>
+      <c r="D165" s="27" t="n"/>
       <c r="E165" s="15" t="n"/>
       <c r="F165" s="16" t="n"/>
       <c r="G165" s="16" t="n"/>
@@ -12865,7 +12867,7 @@
       <c r="A166" s="20" t="n"/>
       <c r="B166" s="21" t="n"/>
       <c r="C166" s="21" t="n"/>
-      <c r="D166" s="21" t="n"/>
+      <c r="D166" s="28" t="n"/>
       <c r="E166" s="22" t="n"/>
       <c r="F166" s="23" t="n"/>
       <c r="G166" s="23" t="n"/>
@@ -12890,7 +12892,7 @@
       <c r="A167" s="13" t="n"/>
       <c r="B167" s="14" t="n"/>
       <c r="C167" s="14" t="n"/>
-      <c r="D167" s="14" t="n"/>
+      <c r="D167" s="27" t="n"/>
       <c r="E167" s="15" t="n"/>
       <c r="F167" s="16" t="n"/>
       <c r="G167" s="16" t="n"/>
@@ -12915,7 +12917,7 @@
       <c r="A168" s="20" t="n"/>
       <c r="B168" s="21" t="n"/>
       <c r="C168" s="21" t="n"/>
-      <c r="D168" s="21" t="n"/>
+      <c r="D168" s="28" t="n"/>
       <c r="E168" s="22" t="n"/>
       <c r="F168" s="23" t="n"/>
       <c r="G168" s="23" t="n"/>
@@ -12940,7 +12942,7 @@
       <c r="A169" s="13" t="n"/>
       <c r="B169" s="14" t="n"/>
       <c r="C169" s="14" t="n"/>
-      <c r="D169" s="14" t="n"/>
+      <c r="D169" s="27" t="n"/>
       <c r="E169" s="15" t="n"/>
       <c r="F169" s="16" t="n"/>
       <c r="G169" s="16" t="n"/>
@@ -12965,7 +12967,7 @@
       <c r="A170" s="20" t="n"/>
       <c r="B170" s="21" t="n"/>
       <c r="C170" s="21" t="n"/>
-      <c r="D170" s="21" t="n"/>
+      <c r="D170" s="28" t="n"/>
       <c r="E170" s="22" t="n"/>
       <c r="F170" s="23" t="n"/>
       <c r="G170" s="23" t="n"/>
@@ -12990,7 +12992,7 @@
       <c r="A171" s="13" t="n"/>
       <c r="B171" s="14" t="n"/>
       <c r="C171" s="14" t="n"/>
-      <c r="D171" s="14" t="n"/>
+      <c r="D171" s="27" t="n"/>
       <c r="E171" s="15" t="n"/>
       <c r="F171" s="16" t="n"/>
       <c r="G171" s="16" t="n"/>
@@ -13015,7 +13017,7 @@
       <c r="A172" s="20" t="n"/>
       <c r="B172" s="21" t="n"/>
       <c r="C172" s="21" t="n"/>
-      <c r="D172" s="21" t="n"/>
+      <c r="D172" s="28" t="n"/>
       <c r="E172" s="22" t="n"/>
       <c r="F172" s="23" t="n"/>
       <c r="G172" s="23" t="n"/>
@@ -13040,7 +13042,7 @@
       <c r="A173" s="13" t="n"/>
       <c r="B173" s="14" t="n"/>
       <c r="C173" s="14" t="n"/>
-      <c r="D173" s="14" t="n"/>
+      <c r="D173" s="27" t="n"/>
       <c r="E173" s="15" t="n"/>
       <c r="F173" s="16" t="n"/>
       <c r="G173" s="16" t="n"/>
@@ -13065,7 +13067,7 @@
       <c r="A174" s="20" t="n"/>
       <c r="B174" s="21" t="n"/>
       <c r="C174" s="21" t="n"/>
-      <c r="D174" s="21" t="n"/>
+      <c r="D174" s="28" t="n"/>
       <c r="E174" s="22" t="n"/>
       <c r="F174" s="23" t="n"/>
       <c r="G174" s="23" t="n"/>
@@ -13090,7 +13092,7 @@
       <c r="A175" s="13" t="n"/>
       <c r="B175" s="14" t="n"/>
       <c r="C175" s="14" t="n"/>
-      <c r="D175" s="14" t="n"/>
+      <c r="D175" s="27" t="n"/>
       <c r="E175" s="15" t="n"/>
       <c r="F175" s="16" t="n"/>
       <c r="G175" s="16" t="n"/>
@@ -13115,7 +13117,7 @@
       <c r="A176" s="20" t="n"/>
       <c r="B176" s="21" t="n"/>
       <c r="C176" s="21" t="n"/>
-      <c r="D176" s="21" t="n"/>
+      <c r="D176" s="28" t="n"/>
       <c r="E176" s="22" t="n"/>
       <c r="F176" s="23" t="n"/>
       <c r="G176" s="23" t="n"/>
@@ -13140,7 +13142,7 @@
       <c r="A177" s="13" t="n"/>
       <c r="B177" s="14" t="n"/>
       <c r="C177" s="14" t="n"/>
-      <c r="D177" s="14" t="n"/>
+      <c r="D177" s="27" t="n"/>
       <c r="E177" s="15" t="n"/>
       <c r="F177" s="16" t="n"/>
       <c r="G177" s="16" t="n"/>
@@ -13165,7 +13167,7 @@
       <c r="A178" s="20" t="n"/>
       <c r="B178" s="21" t="n"/>
       <c r="C178" s="21" t="n"/>
-      <c r="D178" s="21" t="n"/>
+      <c r="D178" s="28" t="n"/>
       <c r="E178" s="22" t="n"/>
       <c r="F178" s="23" t="n"/>
       <c r="G178" s="23" t="n"/>
@@ -13190,7 +13192,7 @@
       <c r="A179" s="13" t="n"/>
       <c r="B179" s="14" t="n"/>
       <c r="C179" s="14" t="n"/>
-      <c r="D179" s="14" t="n"/>
+      <c r="D179" s="27" t="n"/>
       <c r="E179" s="15" t="n"/>
       <c r="F179" s="16" t="n"/>
       <c r="G179" s="16" t="n"/>
@@ -13215,7 +13217,7 @@
       <c r="A180" s="20" t="n"/>
       <c r="B180" s="21" t="n"/>
       <c r="C180" s="21" t="n"/>
-      <c r="D180" s="21" t="n"/>
+      <c r="D180" s="28" t="n"/>
       <c r="E180" s="22" t="n"/>
       <c r="F180" s="23" t="n"/>
       <c r="G180" s="23" t="n"/>
@@ -13240,7 +13242,7 @@
       <c r="A181" s="13" t="n"/>
       <c r="B181" s="14" t="n"/>
       <c r="C181" s="14" t="n"/>
-      <c r="D181" s="14" t="n"/>
+      <c r="D181" s="27" t="n"/>
       <c r="E181" s="15" t="n"/>
       <c r="F181" s="16" t="n"/>
       <c r="G181" s="16" t="n"/>
@@ -13265,7 +13267,7 @@
       <c r="A182" s="20" t="n"/>
       <c r="B182" s="21" t="n"/>
       <c r="C182" s="21" t="n"/>
-      <c r="D182" s="21" t="n"/>
+      <c r="D182" s="28" t="n"/>
       <c r="E182" s="22" t="n"/>
       <c r="F182" s="23" t="n"/>
       <c r="G182" s="23" t="n"/>
@@ -13290,7 +13292,7 @@
       <c r="A183" s="13" t="n"/>
       <c r="B183" s="14" t="n"/>
       <c r="C183" s="14" t="n"/>
-      <c r="D183" s="14" t="n"/>
+      <c r="D183" s="27" t="n"/>
       <c r="E183" s="15" t="n"/>
       <c r="F183" s="16" t="n"/>
       <c r="G183" s="16" t="n"/>
@@ -13315,7 +13317,7 @@
       <c r="A184" s="20" t="n"/>
       <c r="B184" s="21" t="n"/>
       <c r="C184" s="21" t="n"/>
-      <c r="D184" s="21" t="n"/>
+      <c r="D184" s="28" t="n"/>
       <c r="E184" s="22" t="n"/>
       <c r="F184" s="23" t="n"/>
       <c r="G184" s="23" t="n"/>
@@ -13340,7 +13342,7 @@
       <c r="A185" s="13" t="n"/>
       <c r="B185" s="14" t="n"/>
       <c r="C185" s="14" t="n"/>
-      <c r="D185" s="14" t="n"/>
+      <c r="D185" s="27" t="n"/>
       <c r="E185" s="15" t="n"/>
       <c r="F185" s="16" t="n"/>
       <c r="G185" s="16" t="n"/>
@@ -13365,7 +13367,7 @@
       <c r="A186" s="20" t="n"/>
       <c r="B186" s="21" t="n"/>
       <c r="C186" s="21" t="n"/>
-      <c r="D186" s="21" t="n"/>
+      <c r="D186" s="28" t="n"/>
       <c r="E186" s="22" t="n"/>
       <c r="F186" s="23" t="n"/>
       <c r="G186" s="23" t="n"/>
@@ -13390,7 +13392,7 @@
       <c r="A187" s="13" t="n"/>
       <c r="B187" s="14" t="n"/>
       <c r="C187" s="14" t="n"/>
-      <c r="D187" s="14" t="n"/>
+      <c r="D187" s="27" t="n"/>
       <c r="E187" s="15" t="n"/>
       <c r="F187" s="16" t="n"/>
       <c r="G187" s="16" t="n"/>
@@ -13415,7 +13417,7 @@
       <c r="A188" s="20" t="n"/>
       <c r="B188" s="21" t="n"/>
       <c r="C188" s="21" t="n"/>
-      <c r="D188" s="21" t="n"/>
+      <c r="D188" s="28" t="n"/>
       <c r="E188" s="22" t="n"/>
       <c r="F188" s="23" t="n"/>
       <c r="G188" s="23" t="n"/>
@@ -13440,7 +13442,7 @@
       <c r="A189" s="13" t="n"/>
       <c r="B189" s="14" t="n"/>
       <c r="C189" s="14" t="n"/>
-      <c r="D189" s="14" t="n"/>
+      <c r="D189" s="27" t="n"/>
       <c r="E189" s="15" t="n"/>
       <c r="F189" s="16" t="n"/>
       <c r="G189" s="16" t="n"/>
@@ -13465,7 +13467,7 @@
       <c r="A190" s="20" t="n"/>
       <c r="B190" s="21" t="n"/>
       <c r="C190" s="21" t="n"/>
-      <c r="D190" s="21" t="n"/>
+      <c r="D190" s="28" t="n"/>
       <c r="E190" s="22" t="n"/>
       <c r="F190" s="23" t="n"/>
       <c r="G190" s="23" t="n"/>
@@ -13490,7 +13492,7 @@
       <c r="A191" s="13" t="n"/>
       <c r="B191" s="14" t="n"/>
       <c r="C191" s="14" t="n"/>
-      <c r="D191" s="14" t="n"/>
+      <c r="D191" s="27" t="n"/>
       <c r="E191" s="15" t="n"/>
       <c r="F191" s="16" t="n"/>
       <c r="G191" s="16" t="n"/>
@@ -13515,7 +13517,7 @@
       <c r="A192" s="20" t="n"/>
       <c r="B192" s="21" t="n"/>
       <c r="C192" s="21" t="n"/>
-      <c r="D192" s="21" t="n"/>
+      <c r="D192" s="28" t="n"/>
       <c r="E192" s="22" t="n"/>
       <c r="F192" s="23" t="n"/>
       <c r="G192" s="23" t="n"/>
@@ -13540,7 +13542,7 @@
       <c r="A193" s="13" t="n"/>
       <c r="B193" s="14" t="n"/>
       <c r="C193" s="14" t="n"/>
-      <c r="D193" s="14" t="n"/>
+      <c r="D193" s="27" t="n"/>
       <c r="E193" s="15" t="n"/>
       <c r="F193" s="16" t="n"/>
       <c r="G193" s="16" t="n"/>
@@ -13565,7 +13567,7 @@
       <c r="A194" s="20" t="n"/>
       <c r="B194" s="21" t="n"/>
       <c r="C194" s="21" t="n"/>
-      <c r="D194" s="21" t="n"/>
+      <c r="D194" s="28" t="n"/>
       <c r="E194" s="22" t="n"/>
       <c r="F194" s="23" t="n"/>
       <c r="G194" s="23" t="n"/>
@@ -13590,7 +13592,7 @@
       <c r="A195" s="13" t="n"/>
       <c r="B195" s="14" t="n"/>
       <c r="C195" s="14" t="n"/>
-      <c r="D195" s="14" t="n"/>
+      <c r="D195" s="27" t="n"/>
       <c r="E195" s="15" t="n"/>
       <c r="F195" s="16" t="n"/>
       <c r="G195" s="16" t="n"/>
@@ -13615,7 +13617,7 @@
       <c r="A196" s="20" t="n"/>
       <c r="B196" s="21" t="n"/>
       <c r="C196" s="21" t="n"/>
-      <c r="D196" s="21" t="n"/>
+      <c r="D196" s="28" t="n"/>
       <c r="E196" s="22" t="n"/>
       <c r="F196" s="23" t="n"/>
       <c r="G196" s="23" t="n"/>
@@ -13640,7 +13642,7 @@
       <c r="A197" s="13" t="n"/>
       <c r="B197" s="14" t="n"/>
       <c r="C197" s="14" t="n"/>
-      <c r="D197" s="14" t="n"/>
+      <c r="D197" s="27" t="n"/>
       <c r="E197" s="15" t="n"/>
       <c r="F197" s="16" t="n"/>
       <c r="G197" s="16" t="n"/>
@@ -13665,7 +13667,7 @@
       <c r="A198" s="20" t="n"/>
       <c r="B198" s="21" t="n"/>
       <c r="C198" s="21" t="n"/>
-      <c r="D198" s="21" t="n"/>
+      <c r="D198" s="28" t="n"/>
       <c r="E198" s="22" t="n"/>
       <c r="F198" s="23" t="n"/>
       <c r="G198" s="23" t="n"/>
@@ -13690,7 +13692,7 @@
       <c r="A199" s="13" t="n"/>
       <c r="B199" s="14" t="n"/>
       <c r="C199" s="14" t="n"/>
-      <c r="D199" s="14" t="n"/>
+      <c r="D199" s="27" t="n"/>
       <c r="E199" s="15" t="n"/>
       <c r="F199" s="16" t="n"/>
       <c r="G199" s="16" t="n"/>
@@ -13715,7 +13717,7 @@
       <c r="A200" s="20" t="n"/>
       <c r="B200" s="21" t="n"/>
       <c r="C200" s="21" t="n"/>
-      <c r="D200" s="21" t="n"/>
+      <c r="D200" s="28" t="n"/>
       <c r="E200" s="22" t="n"/>
       <c r="F200" s="23" t="n"/>
       <c r="G200" s="23" t="n"/>
@@ -13740,7 +13742,7 @@
       <c r="A201" s="13" t="n"/>
       <c r="B201" s="14" t="n"/>
       <c r="C201" s="14" t="n"/>
-      <c r="D201" s="14" t="n"/>
+      <c r="D201" s="27" t="n"/>
       <c r="E201" s="15" t="n"/>
       <c r="F201" s="16" t="n"/>
       <c r="G201" s="16" t="n"/>
@@ -13765,7 +13767,7 @@
       <c r="A202" s="20" t="n"/>
       <c r="B202" s="21" t="n"/>
       <c r="C202" s="21" t="n"/>
-      <c r="D202" s="21" t="n"/>
+      <c r="D202" s="28" t="n"/>
       <c r="E202" s="22" t="n"/>
       <c r="F202" s="23" t="n"/>
       <c r="G202" s="23" t="n"/>
@@ -13790,7 +13792,7 @@
       <c r="A203" s="13" t="n"/>
       <c r="B203" s="14" t="n"/>
       <c r="C203" s="14" t="n"/>
-      <c r="D203" s="14" t="n"/>
+      <c r="D203" s="27" t="n"/>
       <c r="E203" s="15" t="n"/>
       <c r="F203" s="16" t="n"/>
       <c r="G203" s="16" t="n"/>
@@ -13815,7 +13817,7 @@
       <c r="A204" s="20" t="n"/>
       <c r="B204" s="21" t="n"/>
       <c r="C204" s="21" t="n"/>
-      <c r="D204" s="21" t="n"/>
+      <c r="D204" s="28" t="n"/>
       <c r="E204" s="22" t="n"/>
       <c r="F204" s="23" t="n"/>
       <c r="G204" s="23" t="n"/>
@@ -13840,7 +13842,7 @@
       <c r="A205" s="13" t="n"/>
       <c r="B205" s="14" t="n"/>
       <c r="C205" s="14" t="n"/>
-      <c r="D205" s="14" t="n"/>
+      <c r="D205" s="27" t="n"/>
       <c r="E205" s="15" t="n"/>
       <c r="F205" s="16" t="n"/>
       <c r="G205" s="16" t="n"/>
@@ -13865,7 +13867,7 @@
       <c r="A206" s="20" t="n"/>
       <c r="B206" s="21" t="n"/>
       <c r="C206" s="21" t="n"/>
-      <c r="D206" s="21" t="n"/>
+      <c r="D206" s="28" t="n"/>
       <c r="E206" s="22" t="n"/>
       <c r="F206" s="23" t="n"/>
       <c r="G206" s="23" t="n"/>
@@ -13890,7 +13892,7 @@
       <c r="A207" s="13" t="n"/>
       <c r="B207" s="14" t="n"/>
       <c r="C207" s="14" t="n"/>
-      <c r="D207" s="14" t="n"/>
+      <c r="D207" s="27" t="n"/>
       <c r="E207" s="15" t="n"/>
       <c r="F207" s="16" t="n"/>
       <c r="G207" s="16" t="n"/>
@@ -13915,7 +13917,7 @@
       <c r="A208" s="20" t="n"/>
       <c r="B208" s="21" t="n"/>
       <c r="C208" s="21" t="n"/>
-      <c r="D208" s="21" t="n"/>
+      <c r="D208" s="28" t="n"/>
       <c r="E208" s="22" t="n"/>
       <c r="F208" s="23" t="n"/>
       <c r="G208" s="23" t="n"/>
@@ -13940,7 +13942,7 @@
       <c r="A209" s="13" t="n"/>
       <c r="B209" s="14" t="n"/>
       <c r="C209" s="14" t="n"/>
-      <c r="D209" s="14" t="n"/>
+      <c r="D209" s="27" t="n"/>
       <c r="E209" s="15" t="n"/>
       <c r="F209" s="16" t="n"/>
       <c r="G209" s="16" t="n"/>
@@ -13965,7 +13967,7 @@
       <c r="A210" s="20" t="n"/>
       <c r="B210" s="21" t="n"/>
       <c r="C210" s="21" t="n"/>
-      <c r="D210" s="21" t="n"/>
+      <c r="D210" s="28" t="n"/>
       <c r="E210" s="22" t="n"/>
       <c r="F210" s="23" t="n"/>
       <c r="G210" s="23" t="n"/>
@@ -13990,7 +13992,7 @@
       <c r="A211" s="13" t="n"/>
       <c r="B211" s="14" t="n"/>
       <c r="C211" s="14" t="n"/>
-      <c r="D211" s="14" t="n"/>
+      <c r="D211" s="27" t="n"/>
       <c r="E211" s="15" t="n"/>
       <c r="F211" s="16" t="n"/>
       <c r="G211" s="16" t="n"/>
@@ -14015,7 +14017,7 @@
       <c r="A212" s="20" t="n"/>
       <c r="B212" s="21" t="n"/>
       <c r="C212" s="21" t="n"/>
-      <c r="D212" s="21" t="n"/>
+      <c r="D212" s="28" t="n"/>
       <c r="E212" s="22" t="n"/>
       <c r="F212" s="23" t="n"/>
       <c r="G212" s="23" t="n"/>
@@ -14040,7 +14042,7 @@
       <c r="A213" s="13" t="n"/>
       <c r="B213" s="14" t="n"/>
       <c r="C213" s="14" t="n"/>
-      <c r="D213" s="14" t="n"/>
+      <c r="D213" s="27" t="n"/>
       <c r="E213" s="15" t="n"/>
       <c r="F213" s="16" t="n"/>
       <c r="G213" s="16" t="n"/>
@@ -14065,7 +14067,7 @@
       <c r="A214" s="20" t="n"/>
       <c r="B214" s="21" t="n"/>
       <c r="C214" s="21" t="n"/>
-      <c r="D214" s="21" t="n"/>
+      <c r="D214" s="28" t="n"/>
       <c r="E214" s="22" t="n"/>
       <c r="F214" s="23" t="n"/>
       <c r="G214" s="23" t="n"/>
@@ -14090,7 +14092,7 @@
       <c r="A215" s="13" t="n"/>
       <c r="B215" s="14" t="n"/>
       <c r="C215" s="14" t="n"/>
-      <c r="D215" s="14" t="n"/>
+      <c r="D215" s="27" t="n"/>
       <c r="E215" s="15" t="n"/>
       <c r="F215" s="16" t="n"/>
       <c r="G215" s="16" t="n"/>
@@ -14115,7 +14117,7 @@
       <c r="A216" s="20" t="n"/>
       <c r="B216" s="21" t="n"/>
       <c r="C216" s="21" t="n"/>
-      <c r="D216" s="21" t="n"/>
+      <c r="D216" s="28" t="n"/>
       <c r="E216" s="22" t="n"/>
       <c r="F216" s="23" t="n"/>
       <c r="G216" s="23" t="n"/>
@@ -14140,7 +14142,7 @@
       <c r="A217" s="13" t="n"/>
       <c r="B217" s="14" t="n"/>
       <c r="C217" s="14" t="n"/>
-      <c r="D217" s="14" t="n"/>
+      <c r="D217" s="27" t="n"/>
       <c r="E217" s="15" t="n"/>
       <c r="F217" s="16" t="n"/>
       <c r="G217" s="16" t="n"/>
@@ -14165,7 +14167,7 @@
       <c r="A218" s="20" t="n"/>
       <c r="B218" s="21" t="n"/>
       <c r="C218" s="21" t="n"/>
-      <c r="D218" s="21" t="n"/>
+      <c r="D218" s="28" t="n"/>
       <c r="E218" s="22" t="n"/>
       <c r="F218" s="23" t="n"/>
       <c r="G218" s="23" t="n"/>
@@ -14190,7 +14192,7 @@
       <c r="A219" s="13" t="n"/>
       <c r="B219" s="14" t="n"/>
       <c r="C219" s="14" t="n"/>
-      <c r="D219" s="14" t="n"/>
+      <c r="D219" s="27" t="n"/>
       <c r="E219" s="15" t="n"/>
       <c r="F219" s="16" t="n"/>
       <c r="G219" s="16" t="n"/>
@@ -14215,7 +14217,7 @@
       <c r="A220" s="20" t="n"/>
       <c r="B220" s="21" t="n"/>
       <c r="C220" s="21" t="n"/>
-      <c r="D220" s="21" t="n"/>
+      <c r="D220" s="28" t="n"/>
       <c r="E220" s="22" t="n"/>
       <c r="F220" s="23" t="n"/>
       <c r="G220" s="23" t="n"/>
@@ -14240,7 +14242,7 @@
       <c r="A221" s="13" t="n"/>
       <c r="B221" s="14" t="n"/>
       <c r="C221" s="14" t="n"/>
-      <c r="D221" s="14" t="n"/>
+      <c r="D221" s="27" t="n"/>
       <c r="E221" s="15" t="n"/>
       <c r="F221" s="16" t="n"/>
       <c r="G221" s="16" t="n"/>
@@ -14265,7 +14267,7 @@
       <c r="A222" s="20" t="n"/>
       <c r="B222" s="21" t="n"/>
       <c r="C222" s="21" t="n"/>
-      <c r="D222" s="21" t="n"/>
+      <c r="D222" s="28" t="n"/>
       <c r="E222" s="22" t="n"/>
       <c r="F222" s="23" t="n"/>
       <c r="G222" s="23" t="n"/>
@@ -14290,7 +14292,7 @@
       <c r="A223" s="13" t="n"/>
       <c r="B223" s="14" t="n"/>
       <c r="C223" s="14" t="n"/>
-      <c r="D223" s="14" t="n"/>
+      <c r="D223" s="27" t="n"/>
       <c r="E223" s="15" t="n"/>
       <c r="F223" s="16" t="n"/>
       <c r="G223" s="16" t="n"/>
@@ -14315,7 +14317,7 @@
       <c r="A224" s="20" t="n"/>
       <c r="B224" s="21" t="n"/>
       <c r="C224" s="21" t="n"/>
-      <c r="D224" s="21" t="n"/>
+      <c r="D224" s="28" t="n"/>
       <c r="E224" s="22" t="n"/>
       <c r="F224" s="23" t="n"/>
       <c r="G224" s="23" t="n"/>
@@ -14340,7 +14342,7 @@
       <c r="A225" s="13" t="n"/>
       <c r="B225" s="14" t="n"/>
       <c r="C225" s="14" t="n"/>
-      <c r="D225" s="14" t="n"/>
+      <c r="D225" s="27" t="n"/>
       <c r="E225" s="15" t="n"/>
       <c r="F225" s="16" t="n"/>
       <c r="G225" s="16" t="n"/>
@@ -14365,7 +14367,7 @@
       <c r="A226" s="20" t="n"/>
       <c r="B226" s="21" t="n"/>
       <c r="C226" s="21" t="n"/>
-      <c r="D226" s="21" t="n"/>
+      <c r="D226" s="28" t="n"/>
       <c r="E226" s="22" t="n"/>
       <c r="F226" s="23" t="n"/>
       <c r="G226" s="23" t="n"/>
@@ -14390,7 +14392,7 @@
       <c r="A227" s="13" t="n"/>
       <c r="B227" s="14" t="n"/>
       <c r="C227" s="14" t="n"/>
-      <c r="D227" s="14" t="n"/>
+      <c r="D227" s="27" t="n"/>
       <c r="E227" s="15" t="n"/>
       <c r="F227" s="16" t="n"/>
       <c r="G227" s="16" t="n"/>
@@ -14415,7 +14417,7 @@
       <c r="A228" s="20" t="n"/>
       <c r="B228" s="21" t="n"/>
       <c r="C228" s="21" t="n"/>
-      <c r="D228" s="21" t="n"/>
+      <c r="D228" s="28" t="n"/>
       <c r="E228" s="22" t="n"/>
       <c r="F228" s="23" t="n"/>
       <c r="G228" s="23" t="n"/>
@@ -14440,7 +14442,7 @@
       <c r="A229" s="13" t="n"/>
       <c r="B229" s="14" t="n"/>
       <c r="C229" s="14" t="n"/>
-      <c r="D229" s="14" t="n"/>
+      <c r="D229" s="27" t="n"/>
       <c r="E229" s="15" t="n"/>
       <c r="F229" s="16" t="n"/>
       <c r="G229" s="16" t="n"/>
@@ -14465,7 +14467,7 @@
       <c r="A230" s="20" t="n"/>
       <c r="B230" s="21" t="n"/>
       <c r="C230" s="21" t="n"/>
-      <c r="D230" s="21" t="n"/>
+      <c r="D230" s="28" t="n"/>
       <c r="E230" s="22" t="n"/>
       <c r="F230" s="23" t="n"/>
       <c r="G230" s="23" t="n"/>
@@ -14490,7 +14492,7 @@
       <c r="A231" s="13" t="n"/>
       <c r="B231" s="14" t="n"/>
       <c r="C231" s="14" t="n"/>
-      <c r="D231" s="14" t="n"/>
+      <c r="D231" s="27" t="n"/>
       <c r="E231" s="15" t="n"/>
       <c r="F231" s="16" t="n"/>
       <c r="G231" s="16" t="n"/>
@@ -14515,7 +14517,7 @@
       <c r="A232" s="20" t="n"/>
       <c r="B232" s="21" t="n"/>
       <c r="C232" s="21" t="n"/>
-      <c r="D232" s="21" t="n"/>
+      <c r="D232" s="28" t="n"/>
       <c r="E232" s="22" t="n"/>
       <c r="F232" s="23" t="n"/>
       <c r="G232" s="23" t="n"/>
@@ -14540,7 +14542,7 @@
       <c r="A233" s="13" t="n"/>
       <c r="B233" s="14" t="n"/>
       <c r="C233" s="14" t="n"/>
-      <c r="D233" s="14" t="n"/>
+      <c r="D233" s="27" t="n"/>
       <c r="E233" s="15" t="n"/>
       <c r="F233" s="16" t="n"/>
       <c r="G233" s="16" t="n"/>
@@ -14565,7 +14567,7 @@
       <c r="A234" s="20" t="n"/>
       <c r="B234" s="21" t="n"/>
       <c r="C234" s="21" t="n"/>
-      <c r="D234" s="21" t="n"/>
+      <c r="D234" s="28" t="n"/>
       <c r="E234" s="22" t="n"/>
       <c r="F234" s="23" t="n"/>
       <c r="G234" s="23" t="n"/>
@@ -14590,7 +14592,7 @@
       <c r="A235" s="13" t="n"/>
       <c r="B235" s="14" t="n"/>
       <c r="C235" s="14" t="n"/>
-      <c r="D235" s="14" t="n"/>
+      <c r="D235" s="27" t="n"/>
       <c r="E235" s="15" t="n"/>
       <c r="F235" s="16" t="n"/>
       <c r="G235" s="16" t="n"/>
@@ -14615,7 +14617,7 @@
       <c r="A236" s="20" t="n"/>
       <c r="B236" s="21" t="n"/>
       <c r="C236" s="21" t="n"/>
-      <c r="D236" s="21" t="n"/>
+      <c r="D236" s="28" t="n"/>
       <c r="E236" s="22" t="n"/>
       <c r="F236" s="23" t="n"/>
       <c r="G236" s="23" t="n"/>
@@ -14640,7 +14642,7 @@
       <c r="A237" s="13" t="n"/>
       <c r="B237" s="14" t="n"/>
       <c r="C237" s="14" t="n"/>
-      <c r="D237" s="14" t="n"/>
+      <c r="D237" s="27" t="n"/>
       <c r="E237" s="15" t="n"/>
       <c r="F237" s="16" t="n"/>
       <c r="G237" s="16" t="n"/>
@@ -14665,7 +14667,7 @@
       <c r="A238" s="20" t="n"/>
       <c r="B238" s="21" t="n"/>
       <c r="C238" s="21" t="n"/>
-      <c r="D238" s="21" t="n"/>
+      <c r="D238" s="28" t="n"/>
       <c r="E238" s="22" t="n"/>
       <c r="F238" s="23" t="n"/>
       <c r="G238" s="23" t="n"/>
@@ -14690,7 +14692,7 @@
       <c r="A239" s="13" t="n"/>
       <c r="B239" s="14" t="n"/>
       <c r="C239" s="14" t="n"/>
-      <c r="D239" s="14" t="n"/>
+      <c r="D239" s="27" t="n"/>
       <c r="E239" s="15" t="n"/>
       <c r="F239" s="16" t="n"/>
       <c r="G239" s="16" t="n"/>
@@ -14715,7 +14717,7 @@
       <c r="A240" s="20" t="n"/>
       <c r="B240" s="21" t="n"/>
       <c r="C240" s="21" t="n"/>
-      <c r="D240" s="21" t="n"/>
+      <c r="D240" s="28" t="n"/>
       <c r="E240" s="22" t="n"/>
       <c r="F240" s="23" t="n"/>
       <c r="G240" s="23" t="n"/>
@@ -14740,7 +14742,7 @@
       <c r="A241" s="13" t="n"/>
       <c r="B241" s="14" t="n"/>
       <c r="C241" s="14" t="n"/>
-      <c r="D241" s="14" t="n"/>
+      <c r="D241" s="27" t="n"/>
       <c r="E241" s="15" t="n"/>
       <c r="F241" s="16" t="n"/>
       <c r="G241" s="16" t="n"/>
@@ -14765,7 +14767,7 @@
       <c r="A242" s="20" t="n"/>
       <c r="B242" s="21" t="n"/>
       <c r="C242" s="21" t="n"/>
-      <c r="D242" s="21" t="n"/>
+      <c r="D242" s="28" t="n"/>
       <c r="E242" s="22" t="n"/>
       <c r="F242" s="23" t="n"/>
       <c r="G242" s="23" t="n"/>
@@ -14790,7 +14792,7 @@
       <c r="A243" s="13" t="n"/>
       <c r="B243" s="14" t="n"/>
       <c r="C243" s="14" t="n"/>
-      <c r="D243" s="14" t="n"/>
+      <c r="D243" s="27" t="n"/>
       <c r="E243" s="15" t="n"/>
       <c r="F243" s="16" t="n"/>
       <c r="G243" s="16" t="n"/>
@@ -14815,7 +14817,7 @@
       <c r="A244" s="20" t="n"/>
       <c r="B244" s="21" t="n"/>
       <c r="C244" s="21" t="n"/>
-      <c r="D244" s="21" t="n"/>
+      <c r="D244" s="28" t="n"/>
       <c r="E244" s="22" t="n"/>
       <c r="F244" s="23" t="n"/>
       <c r="G244" s="23" t="n"/>
@@ -14840,7 +14842,7 @@
       <c r="A245" s="13" t="n"/>
       <c r="B245" s="14" t="n"/>
       <c r="C245" s="14" t="n"/>
-      <c r="D245" s="14" t="n"/>
+      <c r="D245" s="27" t="n"/>
       <c r="E245" s="15" t="n"/>
       <c r="F245" s="16" t="n"/>
       <c r="G245" s="16" t="n"/>
@@ -14865,7 +14867,7 @@
       <c r="A246" s="20" t="n"/>
       <c r="B246" s="21" t="n"/>
       <c r="C246" s="21" t="n"/>
-      <c r="D246" s="21" t="n"/>
+      <c r="D246" s="28" t="n"/>
       <c r="E246" s="22" t="n"/>
       <c r="F246" s="23" t="n"/>
       <c r="G246" s="23" t="n"/>
@@ -14890,7 +14892,7 @@
       <c r="A247" s="13" t="n"/>
       <c r="B247" s="14" t="n"/>
       <c r="C247" s="14" t="n"/>
-      <c r="D247" s="14" t="n"/>
+      <c r="D247" s="27" t="n"/>
       <c r="E247" s="15" t="n"/>
       <c r="F247" s="16" t="n"/>
       <c r="G247" s="16" t="n"/>
@@ -14915,7 +14917,7 @@
       <c r="A248" s="20" t="n"/>
       <c r="B248" s="21" t="n"/>
       <c r="C248" s="21" t="n"/>
-      <c r="D248" s="21" t="n"/>
+      <c r="D248" s="28" t="n"/>
       <c r="E248" s="22" t="n"/>
       <c r="F248" s="23" t="n"/>
       <c r="G248" s="23" t="n"/>
@@ -14940,7 +14942,7 @@
       <c r="A249" s="13" t="n"/>
       <c r="B249" s="14" t="n"/>
       <c r="C249" s="14" t="n"/>
-      <c r="D249" s="14" t="n"/>
+      <c r="D249" s="27" t="n"/>
       <c r="E249" s="15" t="n"/>
       <c r="F249" s="16" t="n"/>
       <c r="G249" s="16" t="n"/>
@@ -14965,7 +14967,7 @@
       <c r="A250" s="20" t="n"/>
       <c r="B250" s="21" t="n"/>
       <c r="C250" s="21" t="n"/>
-      <c r="D250" s="21" t="n"/>
+      <c r="D250" s="28" t="n"/>
       <c r="E250" s="22" t="n"/>
       <c r="F250" s="23" t="n"/>
       <c r="G250" s="23" t="n"/>
@@ -14990,7 +14992,7 @@
       <c r="A251" s="13" t="n"/>
       <c r="B251" s="14" t="n"/>
       <c r="C251" s="14" t="n"/>
-      <c r="D251" s="14" t="n"/>
+      <c r="D251" s="27" t="n"/>
       <c r="E251" s="15" t="n"/>
       <c r="F251" s="16" t="n"/>
       <c r="G251" s="16" t="n"/>
@@ -15015,7 +15017,7 @@
       <c r="A252" s="20" t="n"/>
       <c r="B252" s="21" t="n"/>
       <c r="C252" s="21" t="n"/>
-      <c r="D252" s="21" t="n"/>
+      <c r="D252" s="28" t="n"/>
       <c r="E252" s="22" t="n"/>
       <c r="F252" s="23" t="n"/>
       <c r="G252" s="23" t="n"/>
@@ -15040,7 +15042,7 @@
       <c r="A253" s="13" t="n"/>
       <c r="B253" s="14" t="n"/>
       <c r="C253" s="14" t="n"/>
-      <c r="D253" s="14" t="n"/>
+      <c r="D253" s="27" t="n"/>
       <c r="E253" s="15" t="n"/>
       <c r="F253" s="16" t="n"/>
       <c r="G253" s="16" t="n"/>
@@ -15065,7 +15067,7 @@
       <c r="A254" s="20" t="n"/>
       <c r="B254" s="21" t="n"/>
       <c r="C254" s="21" t="n"/>
-      <c r="D254" s="21" t="n"/>
+      <c r="D254" s="28" t="n"/>
       <c r="E254" s="22" t="n"/>
       <c r="F254" s="23" t="n"/>
       <c r="G254" s="23" t="n"/>
@@ -15090,7 +15092,7 @@
       <c r="A255" s="13" t="n"/>
       <c r="B255" s="14" t="n"/>
       <c r="C255" s="14" t="n"/>
-      <c r="D255" s="14" t="n"/>
+      <c r="D255" s="27" t="n"/>
       <c r="E255" s="15" t="n"/>
       <c r="F255" s="16" t="n"/>
       <c r="G255" s="16" t="n"/>
@@ -15115,7 +15117,7 @@
       <c r="A256" s="20" t="n"/>
       <c r="B256" s="21" t="n"/>
       <c r="C256" s="21" t="n"/>
-      <c r="D256" s="21" t="n"/>
+      <c r="D256" s="28" t="n"/>
       <c r="E256" s="22" t="n"/>
       <c r="F256" s="23" t="n"/>
       <c r="G256" s="23" t="n"/>
@@ -15140,7 +15142,7 @@
       <c r="A257" s="13" t="n"/>
       <c r="B257" s="14" t="n"/>
       <c r="C257" s="14" t="n"/>
-      <c r="D257" s="14" t="n"/>
+      <c r="D257" s="27" t="n"/>
       <c r="E257" s="15" t="n"/>
       <c r="F257" s="16" t="n"/>
       <c r="G257" s="16" t="n"/>
@@ -15165,7 +15167,7 @@
       <c r="A258" s="20" t="n"/>
       <c r="B258" s="21" t="n"/>
       <c r="C258" s="21" t="n"/>
-      <c r="D258" s="21" t="n"/>
+      <c r="D258" s="28" t="n"/>
       <c r="E258" s="22" t="n"/>
       <c r="F258" s="23" t="n"/>
       <c r="G258" s="23" t="n"/>
@@ -15190,7 +15192,7 @@
       <c r="A259" s="13" t="n"/>
       <c r="B259" s="14" t="n"/>
       <c r="C259" s="14" t="n"/>
-      <c r="D259" s="14" t="n"/>
+      <c r="D259" s="27" t="n"/>
       <c r="E259" s="15" t="n"/>
       <c r="F259" s="16" t="n"/>
       <c r="G259" s="16" t="n"/>
@@ -15215,7 +15217,7 @@
       <c r="A260" s="20" t="n"/>
       <c r="B260" s="21" t="n"/>
       <c r="C260" s="21" t="n"/>
-      <c r="D260" s="21" t="n"/>
+      <c r="D260" s="28" t="n"/>
       <c r="E260" s="22" t="n"/>
       <c r="F260" s="23" t="n"/>
       <c r="G260" s="23" t="n"/>
@@ -15240,7 +15242,7 @@
       <c r="A261" s="13" t="n"/>
       <c r="B261" s="14" t="n"/>
       <c r="C261" s="14" t="n"/>
-      <c r="D261" s="14" t="n"/>
+      <c r="D261" s="27" t="n"/>
       <c r="E261" s="15" t="n"/>
       <c r="F261" s="16" t="n"/>
       <c r="G261" s="16" t="n"/>
@@ -15265,7 +15267,7 @@
       <c r="A262" s="20" t="n"/>
       <c r="B262" s="21" t="n"/>
       <c r="C262" s="21" t="n"/>
-      <c r="D262" s="21" t="n"/>
+      <c r="D262" s="28" t="n"/>
       <c r="E262" s="22" t="n"/>
       <c r="F262" s="23" t="n"/>
       <c r="G262" s="23" t="n"/>
@@ -15290,7 +15292,7 @@
       <c r="A263" s="13" t="n"/>
       <c r="B263" s="14" t="n"/>
       <c r="C263" s="14" t="n"/>
-      <c r="D263" s="14" t="n"/>
+      <c r="D263" s="27" t="n"/>
       <c r="E263" s="15" t="n"/>
       <c r="F263" s="16" t="n"/>
       <c r="G263" s="16" t="n"/>
@@ -15315,7 +15317,7 @@
       <c r="A264" s="20" t="n"/>
       <c r="B264" s="21" t="n"/>
       <c r="C264" s="21" t="n"/>
-      <c r="D264" s="21" t="n"/>
+      <c r="D264" s="28" t="n"/>
       <c r="E264" s="22" t="n"/>
       <c r="F264" s="23" t="n"/>
       <c r="G264" s="23" t="n"/>
@@ -15340,7 +15342,7 @@
       <c r="A265" s="13" t="n"/>
       <c r="B265" s="14" t="n"/>
       <c r="C265" s="14" t="n"/>
-      <c r="D265" s="14" t="n"/>
+      <c r="D265" s="27" t="n"/>
       <c r="E265" s="15" t="n"/>
       <c r="F265" s="16" t="n"/>
       <c r="G265" s="16" t="n"/>
@@ -15365,7 +15367,7 @@
       <c r="A266" s="20" t="n"/>
       <c r="B266" s="21" t="n"/>
       <c r="C266" s="21" t="n"/>
-      <c r="D266" s="21" t="n"/>
+      <c r="D266" s="28" t="n"/>
       <c r="E266" s="22" t="n"/>
       <c r="F266" s="23" t="n"/>
       <c r="G266" s="23" t="n"/>
@@ -15390,7 +15392,7 @@
       <c r="A267" s="13" t="n"/>
       <c r="B267" s="14" t="n"/>
       <c r="C267" s="14" t="n"/>
-      <c r="D267" s="14" t="n"/>
+      <c r="D267" s="27" t="n"/>
       <c r="E267" s="15" t="n"/>
       <c r="F267" s="16" t="n"/>
       <c r="G267" s="16" t="n"/>
@@ -15415,7 +15417,7 @@
       <c r="A268" s="20" t="n"/>
       <c r="B268" s="21" t="n"/>
       <c r="C268" s="21" t="n"/>
-      <c r="D268" s="21" t="n"/>
+      <c r="D268" s="28" t="n"/>
       <c r="E268" s="22" t="n"/>
       <c r="F268" s="23" t="n"/>
       <c r="G268" s="23" t="n"/>
@@ -15440,7 +15442,7 @@
       <c r="A269" s="13" t="n"/>
       <c r="B269" s="14" t="n"/>
       <c r="C269" s="14" t="n"/>
-      <c r="D269" s="14" t="n"/>
+      <c r="D269" s="27" t="n"/>
       <c r="E269" s="15" t="n"/>
       <c r="F269" s="16" t="n"/>
       <c r="G269" s="16" t="n"/>
@@ -15465,7 +15467,7 @@
       <c r="A270" s="20" t="n"/>
       <c r="B270" s="21" t="n"/>
       <c r="C270" s="21" t="n"/>
-      <c r="D270" s="21" t="n"/>
+      <c r="D270" s="28" t="n"/>
       <c r="E270" s="22" t="n"/>
       <c r="F270" s="23" t="n"/>
       <c r="G270" s="23" t="n"/>
@@ -15490,7 +15492,7 @@
       <c r="A271" s="13" t="n"/>
       <c r="B271" s="14" t="n"/>
       <c r="C271" s="14" t="n"/>
-      <c r="D271" s="14" t="n"/>
+      <c r="D271" s="27" t="n"/>
       <c r="E271" s="15" t="n"/>
       <c r="F271" s="16" t="n"/>
       <c r="G271" s="16" t="n"/>
@@ -15515,7 +15517,7 @@
       <c r="A272" s="20" t="n"/>
       <c r="B272" s="21" t="n"/>
       <c r="C272" s="21" t="n"/>
-      <c r="D272" s="21" t="n"/>
+      <c r="D272" s="28" t="n"/>
       <c r="E272" s="22" t="n"/>
       <c r="F272" s="23" t="n"/>
       <c r="G272" s="23" t="n"/>
@@ -15540,7 +15542,7 @@
       <c r="A273" s="13" t="n"/>
       <c r="B273" s="14" t="n"/>
       <c r="C273" s="14" t="n"/>
-      <c r="D273" s="14" t="n"/>
+      <c r="D273" s="27" t="n"/>
       <c r="E273" s="15" t="n"/>
       <c r="F273" s="16" t="n"/>
       <c r="G273" s="16" t="n"/>
@@ -15565,7 +15567,7 @@
       <c r="A274" s="20" t="n"/>
       <c r="B274" s="21" t="n"/>
       <c r="C274" s="21" t="n"/>
-      <c r="D274" s="21" t="n"/>
+      <c r="D274" s="28" t="n"/>
       <c r="E274" s="22" t="n"/>
       <c r="F274" s="23" t="n"/>
       <c r="G274" s="23" t="n"/>
@@ -15590,7 +15592,7 @@
       <c r="A275" s="13" t="n"/>
       <c r="B275" s="14" t="n"/>
       <c r="C275" s="14" t="n"/>
-      <c r="D275" s="14" t="n"/>
+      <c r="D275" s="27" t="n"/>
       <c r="E275" s="15" t="n"/>
       <c r="F275" s="16" t="n"/>
       <c r="G275" s="16" t="n"/>
@@ -15615,7 +15617,7 @@
       <c r="A276" s="20" t="n"/>
       <c r="B276" s="21" t="n"/>
       <c r="C276" s="21" t="n"/>
-      <c r="D276" s="21" t="n"/>
+      <c r="D276" s="28" t="n"/>
       <c r="E276" s="22" t="n"/>
       <c r="F276" s="23" t="n"/>
       <c r="G276" s="23" t="n"/>
@@ -15640,7 +15642,7 @@
       <c r="A277" s="13" t="n"/>
       <c r="B277" s="14" t="n"/>
       <c r="C277" s="14" t="n"/>
-      <c r="D277" s="14" t="n"/>
+      <c r="D277" s="27" t="n"/>
       <c r="E277" s="15" t="n"/>
       <c r="F277" s="16" t="n"/>
       <c r="G277" s="16" t="n"/>
@@ -15665,7 +15667,7 @@
       <c r="A278" s="20" t="n"/>
       <c r="B278" s="21" t="n"/>
       <c r="C278" s="21" t="n"/>
-      <c r="D278" s="21" t="n"/>
+      <c r="D278" s="28" t="n"/>
       <c r="E278" s="22" t="n"/>
       <c r="F278" s="23" t="n"/>
       <c r="G278" s="23" t="n"/>
@@ -15690,7 +15692,7 @@
       <c r="A279" s="13" t="n"/>
       <c r="B279" s="14" t="n"/>
       <c r="C279" s="14" t="n"/>
-      <c r="D279" s="14" t="n"/>
+      <c r="D279" s="27" t="n"/>
       <c r="E279" s="15" t="n"/>
       <c r="F279" s="16" t="n"/>
       <c r="G279" s="16" t="n"/>
@@ -15715,7 +15717,7 @@
       <c r="A280" s="20" t="n"/>
       <c r="B280" s="21" t="n"/>
       <c r="C280" s="21" t="n"/>
-      <c r="D280" s="21" t="n"/>
+      <c r="D280" s="28" t="n"/>
       <c r="E280" s="22" t="n"/>
       <c r="F280" s="23" t="n"/>
       <c r="G280" s="23" t="n"/>
@@ -15740,7 +15742,7 @@
       <c r="A281" s="13" t="n"/>
       <c r="B281" s="14" t="n"/>
       <c r="C281" s="14" t="n"/>
-      <c r="D281" s="14" t="n"/>
+      <c r="D281" s="27" t="n"/>
       <c r="E281" s="15" t="n"/>
       <c r="F281" s="16" t="n"/>
       <c r="G281" s="16" t="n"/>
@@ -15765,7 +15767,7 @@
       <c r="A282" s="20" t="n"/>
       <c r="B282" s="21" t="n"/>
       <c r="C282" s="21" t="n"/>
-      <c r="D282" s="21" t="n"/>
+      <c r="D282" s="28" t="n"/>
       <c r="E282" s="22" t="n"/>
       <c r="F282" s="23" t="n"/>
       <c r="G282" s="23" t="n"/>
@@ -15790,7 +15792,7 @@
       <c r="A283" s="13" t="n"/>
       <c r="B283" s="14" t="n"/>
       <c r="C283" s="14" t="n"/>
-      <c r="D283" s="14" t="n"/>
+      <c r="D283" s="27" t="n"/>
       <c r="E283" s="15" t="n"/>
       <c r="F283" s="16" t="n"/>
       <c r="G283" s="16" t="n"/>
@@ -15815,7 +15817,7 @@
       <c r="A284" s="20" t="n"/>
       <c r="B284" s="21" t="n"/>
       <c r="C284" s="21" t="n"/>
-      <c r="D284" s="21" t="n"/>
+      <c r="D284" s="28" t="n"/>
       <c r="E284" s="22" t="n"/>
       <c r="F284" s="23" t="n"/>
       <c r="G284" s="23" t="n"/>
@@ -15840,7 +15842,7 @@
       <c r="A285" s="13" t="n"/>
       <c r="B285" s="14" t="n"/>
       <c r="C285" s="14" t="n"/>
-      <c r="D285" s="14" t="n"/>
+      <c r="D285" s="27" t="n"/>
       <c r="E285" s="15" t="n"/>
       <c r="F285" s="16" t="n"/>
       <c r="G285" s="16" t="n"/>
@@ -15865,7 +15867,7 @@
       <c r="A286" s="20" t="n"/>
       <c r="B286" s="21" t="n"/>
       <c r="C286" s="21" t="n"/>
-      <c r="D286" s="21" t="n"/>
+      <c r="D286" s="28" t="n"/>
       <c r="E286" s="22" t="n"/>
       <c r="F286" s="23" t="n"/>
       <c r="G286" s="23" t="n"/>
@@ -15890,7 +15892,7 @@
       <c r="A287" s="13" t="n"/>
       <c r="B287" s="14" t="n"/>
       <c r="C287" s="14" t="n"/>
-      <c r="D287" s="14" t="n"/>
+      <c r="D287" s="27" t="n"/>
       <c r="E287" s="15" t="n"/>
       <c r="F287" s="16" t="n"/>
       <c r="G287" s="16" t="n"/>
@@ -15915,7 +15917,7 @@
       <c r="A288" s="20" t="n"/>
       <c r="B288" s="21" t="n"/>
       <c r="C288" s="21" t="n"/>
-      <c r="D288" s="21" t="n"/>
+      <c r="D288" s="28" t="n"/>
       <c r="E288" s="22" t="n"/>
       <c r="F288" s="23" t="n"/>
       <c r="G288" s="23" t="n"/>
@@ -15940,7 +15942,7 @@
       <c r="A289" s="13" t="n"/>
       <c r="B289" s="14" t="n"/>
       <c r="C289" s="14" t="n"/>
-      <c r="D289" s="14" t="n"/>
+      <c r="D289" s="27" t="n"/>
       <c r="E289" s="15" t="n"/>
       <c r="F289" s="16" t="n"/>
       <c r="G289" s="16" t="n"/>
@@ -15965,7 +15967,7 @@
       <c r="A290" s="20" t="n"/>
       <c r="B290" s="21" t="n"/>
       <c r="C290" s="21" t="n"/>
-      <c r="D290" s="21" t="n"/>
+      <c r="D290" s="28" t="n"/>
       <c r="E290" s="22" t="n"/>
       <c r="F290" s="23" t="n"/>
       <c r="G290" s="23" t="n"/>
@@ -15990,7 +15992,7 @@
       <c r="A291" s="13" t="n"/>
       <c r="B291" s="14" t="n"/>
       <c r="C291" s="14" t="n"/>
-      <c r="D291" s="14" t="n"/>
+      <c r="D291" s="27" t="n"/>
       <c r="E291" s="15" t="n"/>
       <c r="F291" s="16" t="n"/>
       <c r="G291" s="16" t="n"/>
@@ -16015,7 +16017,7 @@
       <c r="A292" s="20" t="n"/>
       <c r="B292" s="21" t="n"/>
       <c r="C292" s="21" t="n"/>
-      <c r="D292" s="21" t="n"/>
+      <c r="D292" s="28" t="n"/>
       <c r="E292" s="22" t="n"/>
       <c r="F292" s="23" t="n"/>
       <c r="G292" s="23" t="n"/>
@@ -16040,7 +16042,7 @@
       <c r="A293" s="13" t="n"/>
       <c r="B293" s="14" t="n"/>
       <c r="C293" s="14" t="n"/>
-      <c r="D293" s="14" t="n"/>
+      <c r="D293" s="27" t="n"/>
       <c r="E293" s="15" t="n"/>
       <c r="F293" s="16" t="n"/>
       <c r="G293" s="16" t="n"/>
@@ -16065,7 +16067,7 @@
       <c r="A294" s="20" t="n"/>
       <c r="B294" s="21" t="n"/>
       <c r="C294" s="21" t="n"/>
-      <c r="D294" s="21" t="n"/>
+      <c r="D294" s="28" t="n"/>
       <c r="E294" s="22" t="n"/>
       <c r="F294" s="23" t="n"/>
       <c r="G294" s="23" t="n"/>
@@ -16090,7 +16092,7 @@
       <c r="A295" s="13" t="n"/>
       <c r="B295" s="14" t="n"/>
       <c r="C295" s="14" t="n"/>
-      <c r="D295" s="14" t="n"/>
+      <c r="D295" s="27" t="n"/>
       <c r="E295" s="15" t="n"/>
       <c r="F295" s="16" t="n"/>
       <c r="G295" s="16" t="n"/>
@@ -16115,7 +16117,7 @@
       <c r="A296" s="20" t="n"/>
       <c r="B296" s="21" t="n"/>
       <c r="C296" s="21" t="n"/>
-      <c r="D296" s="21" t="n"/>
+      <c r="D296" s="28" t="n"/>
       <c r="E296" s="22" t="n"/>
       <c r="F296" s="23" t="n"/>
       <c r="G296" s="23" t="n"/>
@@ -16140,7 +16142,7 @@
       <c r="A297" s="13" t="n"/>
       <c r="B297" s="14" t="n"/>
       <c r="C297" s="14" t="n"/>
-      <c r="D297" s="14" t="n"/>
+      <c r="D297" s="27" t="n"/>
       <c r="E297" s="15" t="n"/>
       <c r="F297" s="16" t="n"/>
       <c r="G297" s="16" t="n"/>
@@ -16165,7 +16167,7 @@
       <c r="A298" s="20" t="n"/>
       <c r="B298" s="21" t="n"/>
       <c r="C298" s="21" t="n"/>
-      <c r="D298" s="21" t="n"/>
+      <c r="D298" s="28" t="n"/>
       <c r="E298" s="22" t="n"/>
       <c r="F298" s="23" t="n"/>
       <c r="G298" s="23" t="n"/>
@@ -16190,7 +16192,7 @@
       <c r="A299" s="13" t="n"/>
       <c r="B299" s="14" t="n"/>
       <c r="C299" s="14" t="n"/>
-      <c r="D299" s="14" t="n"/>
+      <c r="D299" s="27" t="n"/>
       <c r="E299" s="15" t="n"/>
       <c r="F299" s="16" t="n"/>
       <c r="G299" s="16" t="n"/>
@@ -16215,7 +16217,7 @@
       <c r="A300" s="20" t="n"/>
       <c r="B300" s="21" t="n"/>
       <c r="C300" s="21" t="n"/>
-      <c r="D300" s="21" t="n"/>
+      <c r="D300" s="28" t="n"/>
       <c r="E300" s="22" t="n"/>
       <c r="F300" s="23" t="n"/>
       <c r="G300" s="23" t="n"/>
@@ -16240,7 +16242,7 @@
       <c r="A301" s="13" t="n"/>
       <c r="B301" s="14" t="n"/>
       <c r="C301" s="14" t="n"/>
-      <c r="D301" s="14" t="n"/>
+      <c r="D301" s="27" t="n"/>
       <c r="E301" s="15" t="n"/>
       <c r="F301" s="16" t="n"/>
       <c r="G301" s="16" t="n"/>
@@ -16265,7 +16267,7 @@
       <c r="A302" s="20" t="n"/>
       <c r="B302" s="21" t="n"/>
       <c r="C302" s="21" t="n"/>
-      <c r="D302" s="21" t="n"/>
+      <c r="D302" s="28" t="n"/>
       <c r="E302" s="22" t="n"/>
       <c r="F302" s="23" t="n"/>
       <c r="G302" s="23" t="n"/>
@@ -43298,7 +43300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -43313,7 +43315,7 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="B3" s="27" t="inlineStr"/>
+      <c r="B3" s="29" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -43323,28 +43325,28 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>COMPRAS — cada vez que comprar gado. Preencha data, lote, fornecedor, cabeças, peso e o preço da arroba. As arrobas, o valor e o custo total se calculam sozinhos.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>VENDAS — cada vez que vender. Mesma coisa: o valor líquido já desconta frete e comissão.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>CAIXA — todo dinheiro que entra e sai, inclusive o que não é gado (vacina, sal, diária, combustível). O saldo vai somando linha por linha.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="B8" s="27" t="inlineStr"/>
+      <c r="B8" s="29" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -43354,82 +43356,134 @@
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="B10" s="27" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>PESAGENS — é aqui que cai o que vem do aplicativo Calculadora de Boi. Você também pode digitar à mão se quiser.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="B11" s="27" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>LOTES — junta tudo por lote: quando entrou, quando saiu, quantos dias no pasto, quanto engordou, quanto custou, quanto rendeu e o lucro. Só digite o nome do lote na coluna A — o resto vem sozinho das outras abas.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="B12" s="27" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>PAINEL — o resumo da fazenda. Não mexa, só olhe.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="B13" s="27" t="inlineStr"/>
+      <c r="B13" s="29" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>HISTÓRICO DE CADA ANIMAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>Com a planilha ligada no aplicativo, aparecem mais três abas, montadas sozinhas a partir da PESAGENS: ANIMAIS, HISTÓRICO e CONSULTA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="B16" s="29" t="inlineStr">
+        <is>
+          <t>ANIMAIS — um animal por linha, pelo número do brinco: peso na 1ª pesagem, peso atual, quanto ganhou desde a pesagem anterior, ganho total e ganho por dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="B17" s="29" t="inlineStr">
+        <is>
+          <t>HISTÓRICO — todas as pesagens de cada animal, uma embaixo da outra, da mais antiga pra mais nova.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="B18" s="29" t="inlineStr">
+        <is>
+          <t>CONSULTA — digite o número do brinco na casa amarela e aperte Enter: aparece o resumo e todas as pesagens daquele animal. 010 e 10 são o mesmo brinco.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="B19" s="29" t="inlineStr">
+        <is>
+          <t>Pesou vários bois juntos? Cada um fica com o peso médio da balançada (peso ÷ cabeças). O peso exato de um animal só sai quando ele é pesado sozinho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="B20" s="29" t="inlineStr">
+        <is>
+          <t>Não digite nas abas ANIMAIS e HISTÓRICO: elas são refeitas a cada lote que chega. Corrigiu uma pesagem à mão na PESAGENS? Menu 🐂 Calculadora de Boi → Atualizar histórico dos animais.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="B21" s="29" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>O SEGREDO É O NOME DO LOTE</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="B15" s="27" t="inlineStr">
+    <row r="23" ht="30" customHeight="1">
+      <c r="B23" s="29" t="inlineStr">
         <is>
           <t>Use o MESMO nome de lote nas abas COMPRAS, VENDAS, PESAGENS e CAIXA. É por ele que a planilha junta tudo. Um nome simples resolve: 2026-01 BOI, FAZENDA SÃO LUIZ, LOTE 12.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="B16" s="27" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="2" t="inlineStr">
+    <row r="24" ht="30" customHeight="1">
+      <c r="B24" s="29" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>RENDIMENTO</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="B18" s="27" t="inlineStr">
+    <row r="26" ht="30" customHeight="1">
+      <c r="B26" s="29" t="inlineStr">
         <is>
           <t>Vem preenchido com 52%, que é o comum. Se o seu boi rende diferente, mude na linha — cada linha tem o seu.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="B19" s="27" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="2" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="B27" s="29" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>SE ABRIR NO GOOGLE PLANILHAS</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="27" t="inlineStr">
+    <row r="29" ht="30" customHeight="1">
+      <c r="B29" s="29" t="inlineStr">
         <is>
           <t>Funciona igual: suba o arquivo no Google Drive e abra com Google Planilhas. As fórmulas aparecem traduzidas (SOMASE, SE) automaticamente.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="B22" s="27" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="28" t="inlineStr">
+    <row r="30" ht="30" customHeight="1">
+      <c r="B30" s="29" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="30" t="inlineStr">
         <is>
           <t>THIAGO PORTO 704 AGRO — Compra e venda de bovinos · (77) 99922-6268</t>
         </is>
